--- a/Seasons/Football History.xlsx
+++ b/Seasons/Football History.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mugs&amp;Fred\Documents\Fred\ROSM\Website\public_html\Seasons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFF1673-2268-4E57-8AB6-EDC95D0D6946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF48742A-54A7-4386-80A2-8B30B50518D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A8C7F2BF-BA1F-4802-BC8C-4DC7AFA8B3A8}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="325">
   <si>
     <t>Opponent</t>
   </si>
@@ -105,9 +105,6 @@
     <t>Detroit St. Rose</t>
   </si>
   <si>
-    <t>Grosse Pointe St. Charles</t>
-  </si>
-  <si>
     <t>Ann Arbor St. Thomas</t>
   </si>
   <si>
@@ -163,9 +160,6 @@
   </si>
   <si>
     <t>Highland Park St. Benedict</t>
-  </si>
-  <si>
-    <t>Grosse Point St. Charles</t>
   </si>
   <si>
     <t>3-3-2</t>
@@ -3184,6 +3178,9 @@
       </rPr>
       <t>. The only loss was the 18-0 defeat to the powerful Royal Oak High School football team, which went on to win the Class A Football Championship in 1935. Defense was the cornerstone of the St. Mary football team as they gave up only 7 points in Catholic League play.  The Daily Tribune article on Dec 4 indicated the team banquet was held at Gurnsey's Chop House in Detroit. Coach Janness is the first alumnus to coach St. Mary's football team.</t>
     </r>
+  </si>
+  <si>
+    <t>Detroit St. Charles</t>
   </si>
 </sst>
 </file>
@@ -3642,7 +3639,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3653,7 +3650,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3663,6 +3663,21 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3670,24 +3685,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5184,7 +5181,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="27" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B1" s="25">
         <v>1927</v>
@@ -5193,21 +5190,21 @@
         <v>0</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E1" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F1" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G1" s="26" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
-        <v>168</v>
+      <c r="A2" s="61" t="s">
+        <v>166</v>
       </c>
       <c r="B2" s="2">
         <v>10139</v>
@@ -5224,17 +5221,17 @@
       <c r="F2" s="7">
         <v>0</v>
       </c>
-      <c r="G2" s="52" t="s">
-        <v>254</v>
+      <c r="G2" s="58" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="55"/>
+      <c r="A3" s="61"/>
       <c r="B3" s="2">
         <v>10152</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>5</v>
@@ -5245,10 +5242,10 @@
       <c r="F3" s="7">
         <v>12</v>
       </c>
-      <c r="G3" s="53"/>
+      <c r="G3" s="54"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="55"/>
+      <c r="A4" s="61"/>
       <c r="B4" s="2">
         <v>10156</v>
       </c>
@@ -5264,10 +5261,10 @@
       <c r="F4" s="7">
         <v>14</v>
       </c>
-      <c r="G4" s="53"/>
+      <c r="G4" s="54"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="55"/>
+      <c r="A5" s="61"/>
       <c r="B5" s="2">
         <v>10171</v>
       </c>
@@ -5283,40 +5280,40 @@
       <c r="F5" s="7">
         <v>23</v>
       </c>
-      <c r="G5" s="53"/>
+      <c r="G5" s="54"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="55"/>
+      <c r="A6" s="61"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="6"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="53"/>
+      <c r="G6" s="54"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="55"/>
+      <c r="A7" s="61"/>
       <c r="B7" s="2"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="6"/>
       <c r="F7" s="7"/>
-      <c r="G7" s="53"/>
+      <c r="G7" s="54"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="55"/>
+      <c r="A8" s="61"/>
       <c r="B8" s="2"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="6"/>
       <c r="F8" s="7"/>
-      <c r="G8" s="53"/>
+      <c r="G8" s="54"/>
     </row>
     <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="55"/>
+      <c r="A9" s="61"/>
       <c r="B9" s="2"/>
       <c r="C9" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>23</v>
@@ -5329,11 +5326,11 @@
         <f>SUM(F2:F8)</f>
         <v>49</v>
       </c>
-      <c r="G9" s="54"/>
+      <c r="G9" s="55"/>
     </row>
     <row r="10" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B10" s="10">
         <v>1928</v>
@@ -5342,21 +5339,21 @@
         <v>0</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="55" t="s">
-        <v>170</v>
+      <c r="A11" s="61" t="s">
+        <v>168</v>
       </c>
       <c r="B11" s="2">
         <v>10499</v>
@@ -5373,12 +5370,12 @@
       <c r="F11" s="7">
         <v>0</v>
       </c>
-      <c r="G11" s="52" t="s">
-        <v>283</v>
+      <c r="G11" s="58" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="55"/>
+      <c r="A12" s="61"/>
       <c r="B12" s="2">
         <v>10506</v>
       </c>
@@ -5394,10 +5391,10 @@
       <c r="F12" s="7">
         <v>32</v>
       </c>
-      <c r="G12" s="53"/>
+      <c r="G12" s="54"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="55"/>
+      <c r="A13" s="61"/>
       <c r="B13" s="2">
         <v>10513</v>
       </c>
@@ -5413,10 +5410,10 @@
       <c r="F13" s="7">
         <v>20</v>
       </c>
-      <c r="G13" s="53"/>
+      <c r="G13" s="54"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="55"/>
+      <c r="A14" s="61"/>
       <c r="B14" s="2">
         <v>10527</v>
       </c>
@@ -5432,10 +5429,10 @@
       <c r="F14" s="7">
         <v>19</v>
       </c>
-      <c r="G14" s="53"/>
+      <c r="G14" s="54"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="55"/>
+      <c r="A15" s="61"/>
       <c r="B15" s="2">
         <v>10541</v>
       </c>
@@ -5451,15 +5448,15 @@
       <c r="F15" s="7">
         <v>45</v>
       </c>
-      <c r="G15" s="53"/>
+      <c r="G15" s="54"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="55"/>
+      <c r="A16" s="61"/>
       <c r="B16" s="2">
         <v>10548</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>5</v>
@@ -5470,10 +5467,10 @@
       <c r="F16" s="7">
         <v>7</v>
       </c>
-      <c r="G16" s="53"/>
+      <c r="G16" s="54"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="55"/>
+      <c r="A17" s="61"/>
       <c r="B17" s="2">
         <v>10555</v>
       </c>
@@ -5489,10 +5486,10 @@
       <c r="F17" s="7">
         <v>0</v>
       </c>
-      <c r="G17" s="53"/>
+      <c r="G17" s="54"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="55"/>
+      <c r="A18" s="61"/>
       <c r="B18" s="2">
         <v>10561</v>
       </c>
@@ -5508,13 +5505,13 @@
       <c r="F18" s="7">
         <v>6</v>
       </c>
-      <c r="G18" s="53"/>
+      <c r="G18" s="54"/>
     </row>
     <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="55"/>
+      <c r="A19" s="61"/>
       <c r="B19" s="2"/>
       <c r="C19" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D19" s="17" t="s">
         <v>20</v>
@@ -5527,11 +5524,11 @@
         <f>SUM(F11:F18)</f>
         <v>129</v>
       </c>
-      <c r="G19" s="54"/>
+      <c r="G19" s="55"/>
     </row>
     <row r="20" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B20" s="9">
         <v>1929</v>
@@ -5540,27 +5537,27 @@
         <v>0</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="56" t="s">
-        <v>171</v>
+      <c r="A21" s="62" t="s">
+        <v>169</v>
       </c>
       <c r="B21" s="2">
         <v>10863</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>5</v>
@@ -5571,12 +5568,12 @@
       <c r="F21" s="7">
         <v>27</v>
       </c>
-      <c r="G21" s="52" t="s">
-        <v>294</v>
+      <c r="G21" s="58" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="56"/>
+      <c r="A22" s="62"/>
       <c r="B22" s="2">
         <v>10870</v>
       </c>
@@ -5592,15 +5589,15 @@
       <c r="F22" s="7">
         <v>13</v>
       </c>
-      <c r="G22" s="53"/>
+      <c r="G22" s="54"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="56"/>
+      <c r="A23" s="62"/>
       <c r="B23" s="2">
         <v>10877</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>25</v>
+        <v>324</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>5</v>
@@ -5609,17 +5606,17 @@
         <v>0</v>
       </c>
       <c r="F23" s="7">
-        <v>13</v>
-      </c>
-      <c r="G23" s="53"/>
+        <v>31</v>
+      </c>
+      <c r="G23" s="54"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="56"/>
+      <c r="A24" s="62"/>
       <c r="B24" s="2">
         <v>10884</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>5</v>
@@ -5630,10 +5627,10 @@
       <c r="F24" s="7">
         <v>18</v>
       </c>
-      <c r="G24" s="53"/>
+      <c r="G24" s="54"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="56"/>
+      <c r="A25" s="62"/>
       <c r="B25" s="2">
         <v>10891</v>
       </c>
@@ -5649,10 +5646,10 @@
       <c r="F25" s="7">
         <v>24</v>
       </c>
-      <c r="G25" s="53"/>
+      <c r="G25" s="54"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="56"/>
+      <c r="A26" s="62"/>
       <c r="B26" s="2">
         <v>10898</v>
       </c>
@@ -5668,15 +5665,15 @@
       <c r="F26" s="7">
         <v>7</v>
       </c>
-      <c r="G26" s="53"/>
+      <c r="G26" s="54"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="56"/>
+      <c r="A27" s="62"/>
       <c r="B27" s="2">
         <v>10905</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>4</v>
@@ -5687,15 +5684,15 @@
       <c r="F27" s="7">
         <v>0</v>
       </c>
-      <c r="G27" s="53"/>
+      <c r="G27" s="54"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="56"/>
+      <c r="A28" s="62"/>
       <c r="B28" s="2">
         <v>10912</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>1</v>
@@ -5706,15 +5703,15 @@
       <c r="F28" s="7">
         <v>0</v>
       </c>
-      <c r="G28" s="53"/>
+      <c r="G28" s="54"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="56"/>
+      <c r="A29" s="62"/>
       <c r="B29" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>1</v>
@@ -5725,10 +5722,10 @@
       <c r="F29" s="7">
         <v>0</v>
       </c>
-      <c r="G29" s="53"/>
+      <c r="G29" s="54"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="56"/>
+      <c r="A30" s="62"/>
       <c r="B30" s="2">
         <v>10917</v>
       </c>
@@ -5744,15 +5741,15 @@
       <c r="F30" s="7">
         <v>0</v>
       </c>
-      <c r="G30" s="53"/>
+      <c r="G30" s="54"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="56"/>
+      <c r="A31" s="62"/>
       <c r="B31" s="2">
         <v>10925</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>5</v>
@@ -5763,16 +5760,16 @@
       <c r="F31" s="7">
         <v>7</v>
       </c>
-      <c r="G31" s="53"/>
+      <c r="G31" s="54"/>
     </row>
     <row r="32" spans="1:7" s="29" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="57"/>
+      <c r="A32" s="63"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E32" s="16">
         <f>SUM(E21:E31)</f>
@@ -5780,13 +5777,13 @@
       </c>
       <c r="F32" s="16">
         <f>SUM(F21:F31)</f>
-        <v>109</v>
-      </c>
-      <c r="G32" s="54"/>
+        <v>127</v>
+      </c>
+      <c r="G32" s="55"/>
     </row>
     <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="28" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B33" s="9">
         <v>1930</v>
@@ -5795,13 +5792,13 @@
         <v>0</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G33" s="9" t="s">
         <v>8</v>
@@ -5809,7 +5806,7 @@
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="45" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B34" s="2">
         <v>11227</v>
@@ -5826,8 +5823,8 @@
       <c r="F34" s="7">
         <v>0</v>
       </c>
-      <c r="G34" s="52" t="s">
-        <v>295</v>
+      <c r="G34" s="58" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -5836,7 +5833,7 @@
         <v>11234</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>1</v>
@@ -5847,7 +5844,7 @@
       <c r="F35" s="7">
         <v>0</v>
       </c>
-      <c r="G35" s="53"/>
+      <c r="G35" s="54"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="46"/>
@@ -5855,7 +5852,7 @@
         <v>45575</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>25</v>
+        <v>324</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>1</v>
@@ -5866,7 +5863,7 @@
       <c r="F36" s="7">
         <v>0</v>
       </c>
-      <c r="G36" s="53"/>
+      <c r="G36" s="54"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="46"/>
@@ -5874,7 +5871,7 @@
         <v>11248</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>4</v>
@@ -5885,7 +5882,7 @@
       <c r="F37" s="7">
         <v>0</v>
       </c>
-      <c r="G37" s="53"/>
+      <c r="G37" s="54"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="46"/>
@@ -5893,7 +5890,7 @@
         <v>11255</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>5</v>
@@ -5904,7 +5901,7 @@
       <c r="F38" s="7">
         <v>6</v>
       </c>
-      <c r="G38" s="53"/>
+      <c r="G38" s="54"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="46"/>
@@ -5923,7 +5920,7 @@
       <c r="F39" s="7">
         <v>0</v>
       </c>
-      <c r="G39" s="53"/>
+      <c r="G39" s="54"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="46"/>
@@ -5942,7 +5939,7 @@
       <c r="F40" s="7">
         <v>0</v>
       </c>
-      <c r="G40" s="53"/>
+      <c r="G40" s="54"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="46"/>
@@ -5950,7 +5947,7 @@
         <v>11283</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>1</v>
@@ -5961,7 +5958,7 @@
       <c r="F41" s="7">
         <v>0</v>
       </c>
-      <c r="G41" s="53"/>
+      <c r="G41" s="54"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="46"/>
@@ -5969,7 +5966,7 @@
         <v>11289</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>1</v>
@@ -5980,16 +5977,16 @@
       <c r="F42" s="7">
         <v>0</v>
       </c>
-      <c r="G42" s="53"/>
+      <c r="G42" s="54"/>
     </row>
     <row r="43" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="47"/>
       <c r="B43" s="16"/>
       <c r="C43" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E43" s="16">
         <f>SUM(E34:E42)</f>
@@ -5999,11 +5996,11 @@
         <f>SUM(F34:F42)</f>
         <v>6</v>
       </c>
-      <c r="G43" s="54"/>
+      <c r="G43" s="55"/>
     </row>
     <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="28" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B44" s="9">
         <v>1931</v>
@@ -6012,27 +6009,27 @@
         <v>0</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E44" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G44" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="48" t="s">
-        <v>173</v>
+      <c r="A45" s="60" t="s">
+        <v>171</v>
       </c>
       <c r="B45" s="2">
         <v>11598</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>1</v>
@@ -6044,7 +6041,7 @@
         <v>7</v>
       </c>
       <c r="G45" s="51" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -6053,7 +6050,7 @@
         <v>11605</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>4</v>
@@ -6091,7 +6088,7 @@
         <v>11619</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>1</v>
@@ -6110,7 +6107,7 @@
         <v>11626</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>1</v>
@@ -6148,7 +6145,7 @@
         <v>11640</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>1</v>
@@ -6186,7 +6183,7 @@
         <v>11653</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>4</v>
@@ -6203,10 +6200,10 @@
       <c r="A54" s="50"/>
       <c r="B54" s="3"/>
       <c r="C54" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E54" s="22">
         <f>SUM(E45:E53)</f>
@@ -6220,7 +6217,7 @@
     </row>
     <row r="55" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="28" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B55" s="9">
         <v>1932</v>
@@ -6229,13 +6226,13 @@
         <v>0</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F55" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G55" s="9" t="s">
         <v>8</v>
@@ -6243,7 +6240,7 @@
     </row>
     <row r="56" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="45" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B56" s="2">
         <v>11964</v>
@@ -6261,7 +6258,7 @@
         <v>7</v>
       </c>
       <c r="G56" s="51" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -6270,7 +6267,7 @@
         <v>11969</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>25</v>
+        <v>324</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>1</v>
@@ -6289,7 +6286,7 @@
         <v>11978</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>5</v>
@@ -6308,7 +6305,7 @@
         <v>11983</v>
       </c>
       <c r="C59" s="30" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>5</v>
@@ -6346,7 +6343,7 @@
         <v>11999</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>1</v>
@@ -6365,7 +6362,7 @@
         <v>12004</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>1</v>
@@ -6384,7 +6381,7 @@
         <v>12015</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>5</v>
@@ -6401,10 +6398,10 @@
       <c r="A64" s="47"/>
       <c r="B64" s="3"/>
       <c r="C64" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D64" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E64" s="22">
         <f>SUM(E56:E63)</f>
@@ -6418,7 +6415,7 @@
     </row>
     <row r="65" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="28" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B65" s="9">
         <v>1933</v>
@@ -6427,13 +6424,13 @@
         <v>0</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E65" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F65" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G65" s="9" t="s">
         <v>8</v>
@@ -6441,13 +6438,13 @@
     </row>
     <row r="66" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="45" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B66" s="2">
         <v>12328</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>1</v>
@@ -6459,7 +6456,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="51" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -6468,7 +6465,7 @@
         <v>12335</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>5</v>
@@ -6487,7 +6484,7 @@
         <v>12342</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>25</v>
+        <v>324</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>5</v>
@@ -6506,7 +6503,7 @@
         <v>12349</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>1</v>
@@ -6544,7 +6541,7 @@
         <v>12363</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>1</v>
@@ -6563,7 +6560,7 @@
         <v>12370</v>
       </c>
       <c r="C72" s="30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D72" s="3"/>
       <c r="E72" s="6"/>
@@ -6576,7 +6573,7 @@
         <v>12375</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>1</v>
@@ -6595,7 +6592,7 @@
         <v>12384</v>
       </c>
       <c r="C74" s="30" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>1</v>
@@ -6612,10 +6609,10 @@
       <c r="A75" s="47"/>
       <c r="B75" s="3"/>
       <c r="C75" s="20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E75" s="22">
         <f>SUM(E66:E74)</f>
@@ -6629,7 +6626,7 @@
     </row>
     <row r="76" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="28" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B76" s="9">
         <v>1934</v>
@@ -6638,27 +6635,27 @@
         <v>0</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E76" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F76" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G76" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="59" t="s">
-        <v>176</v>
+      <c r="A77" s="56" t="s">
+        <v>174</v>
       </c>
       <c r="B77" s="2">
         <v>12692</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>1</v>
@@ -6669,17 +6666,17 @@
       <c r="F77" s="7">
         <v>6</v>
       </c>
-      <c r="G77" s="52" t="s">
-        <v>297</v>
+      <c r="G77" s="58" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="58"/>
+      <c r="A78" s="57"/>
       <c r="B78" s="2">
         <v>12699</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>25</v>
+        <v>324</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>1</v>
@@ -6690,15 +6687,15 @@
       <c r="F78" s="7">
         <v>12</v>
       </c>
-      <c r="G78" s="53"/>
+      <c r="G78" s="54"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="58"/>
+      <c r="A79" s="57"/>
       <c r="B79" s="2">
         <v>12705</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>5</v>
@@ -6709,10 +6706,10 @@
       <c r="F79" s="7">
         <v>15</v>
       </c>
-      <c r="G79" s="53"/>
+      <c r="G79" s="54"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="58"/>
+      <c r="A80" s="57"/>
       <c r="B80" s="2">
         <v>12713</v>
       </c>
@@ -6728,15 +6725,15 @@
       <c r="F80" s="7">
         <v>0</v>
       </c>
-      <c r="G80" s="53"/>
+      <c r="G80" s="54"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="58"/>
+      <c r="A81" s="57"/>
       <c r="B81" s="2">
         <v>12720</v>
       </c>
       <c r="C81" s="30" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>1</v>
@@ -6747,15 +6744,15 @@
       <c r="F81" s="7">
         <v>0</v>
       </c>
-      <c r="G81" s="53"/>
+      <c r="G81" s="54"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="58"/>
+      <c r="A82" s="57"/>
       <c r="B82" s="2">
         <v>12727</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>1</v>
@@ -6766,15 +6763,15 @@
       <c r="F82" s="7">
         <v>0</v>
       </c>
-      <c r="G82" s="53"/>
+      <c r="G82" s="54"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="58"/>
+      <c r="A83" s="57"/>
       <c r="B83" s="40">
         <v>12734</v>
       </c>
       <c r="C83" s="41" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D83" s="41" t="s">
         <v>5</v>
@@ -6785,15 +6782,15 @@
       <c r="F83" s="43">
         <v>0</v>
       </c>
-      <c r="G83" s="53"/>
+      <c r="G83" s="54"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="58"/>
+      <c r="A84" s="57"/>
       <c r="B84" s="2">
         <v>12741</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>1</v>
@@ -6804,52 +6801,52 @@
       <c r="F84" s="7">
         <v>0</v>
       </c>
-      <c r="G84" s="53"/>
+      <c r="G84" s="54"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="58"/>
+      <c r="A85" s="57"/>
       <c r="B85" s="2"/>
       <c r="D85" s="3"/>
       <c r="E85" s="6"/>
       <c r="F85" s="7"/>
-      <c r="G85" s="53"/>
+      <c r="G85" s="54"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="58"/>
+      <c r="A86" s="57"/>
       <c r="B86" s="2"/>
       <c r="D86" s="3"/>
       <c r="E86" s="6"/>
       <c r="F86" s="7"/>
-      <c r="G86" s="53"/>
+      <c r="G86" s="54"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="58"/>
+      <c r="A87" s="57"/>
       <c r="B87" s="3"/>
       <c r="C87" s="20"/>
       <c r="D87" s="21"/>
       <c r="E87" s="22"/>
       <c r="F87" s="23"/>
-      <c r="G87" s="53"/>
+      <c r="G87" s="54"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="58"/>
+      <c r="A88" s="57"/>
       <c r="B88" s="35"/>
       <c r="C88" s="39" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D88" s="36"/>
       <c r="E88" s="37"/>
       <c r="F88" s="38"/>
-      <c r="G88" s="53"/>
+      <c r="G88" s="54"/>
     </row>
     <row r="89" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="58"/>
+      <c r="A89" s="57"/>
       <c r="B89" s="35"/>
       <c r="C89" s="20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D89" s="21" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E89" s="22">
         <f>SUM(E77:E88)</f>
@@ -6859,11 +6856,11 @@
         <f>SUM(F77:F88)</f>
         <v>33</v>
       </c>
-      <c r="G89" s="54"/>
+      <c r="G89" s="55"/>
     </row>
     <row r="90" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="28" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B90" s="9">
         <v>1935</v>
@@ -6872,27 +6869,27 @@
         <v>0</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E90" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F90" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G90" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="58" t="s">
-        <v>177</v>
+      <c r="A91" s="57" t="s">
+        <v>175</v>
       </c>
       <c r="B91" s="2">
         <v>13063</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>1</v>
@@ -6904,16 +6901,16 @@
         <v>0</v>
       </c>
       <c r="G91" s="51" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="58"/>
+      <c r="A92" s="57"/>
       <c r="B92" s="2">
         <v>13069</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>5</v>
@@ -6927,12 +6924,12 @@
       <c r="G92" s="51"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="58"/>
+      <c r="A93" s="57"/>
       <c r="B93" s="2">
         <v>13077</v>
       </c>
       <c r="C93" s="30" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>1</v>
@@ -6946,12 +6943,12 @@
       <c r="G93" s="51"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="58"/>
+      <c r="A94" s="57"/>
       <c r="B94" s="2">
         <v>13084</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>1</v>
@@ -6965,7 +6962,7 @@
       <c r="G94" s="51"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="58"/>
+      <c r="A95" s="57"/>
       <c r="B95" s="2">
         <v>13091</v>
       </c>
@@ -6984,7 +6981,7 @@
       <c r="G95" s="51"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="58"/>
+      <c r="A96" s="57"/>
       <c r="B96" s="2">
         <v>13098</v>
       </c>
@@ -7003,12 +7000,12 @@
       <c r="G96" s="51"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="58"/>
+      <c r="A97" s="57"/>
       <c r="B97" s="2">
         <v>13105</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>25</v>
+        <v>324</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>1</v>
@@ -7022,12 +7019,12 @@
       <c r="G97" s="51"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="58"/>
+      <c r="A98" s="57"/>
       <c r="B98" s="2">
         <v>13112</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>4</v>
@@ -7041,10 +7038,10 @@
       <c r="G98" s="51"/>
     </row>
     <row r="99" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="58"/>
+      <c r="A99" s="57"/>
       <c r="B99" s="3"/>
       <c r="C99" s="20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D99" s="21" t="s">
         <v>11</v>
@@ -7061,7 +7058,7 @@
     </row>
     <row r="100" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="28" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B100" s="9">
         <v>1936</v>
@@ -7070,13 +7067,13 @@
         <v>0</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E100" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F100" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G100" s="9" t="s">
         <v>8</v>
@@ -7084,13 +7081,13 @@
     </row>
     <row r="101" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="45" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B101" s="2">
         <v>13420</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>4</v>
@@ -7102,7 +7099,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="51" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -7130,7 +7127,7 @@
         <v>13434</v>
       </c>
       <c r="C103" s="30" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>1</v>
@@ -7149,7 +7146,7 @@
         <v>13441</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>5</v>
@@ -7187,7 +7184,7 @@
         <v>13455</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>1</v>
@@ -7206,7 +7203,7 @@
         <v>13462</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>1</v>
@@ -7225,7 +7222,7 @@
         <v>13469</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>45</v>
+        <v>324</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>5</v>
@@ -7242,10 +7239,10 @@
       <c r="A109" s="47"/>
       <c r="B109" s="3"/>
       <c r="C109" s="20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D109" s="21" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E109" s="22">
         <f>SUM(E101:E108)</f>
@@ -7259,7 +7256,7 @@
     </row>
     <row r="110" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="28" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B110" s="9">
         <v>1937</v>
@@ -7268,13 +7265,13 @@
         <v>0</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E110" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F110" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G110" s="9" t="s">
         <v>8</v>
@@ -7282,13 +7279,13 @@
     </row>
     <row r="111" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="45" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B111" s="2">
         <v>13784</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>5</v>
@@ -7300,7 +7297,7 @@
         <v>13</v>
       </c>
       <c r="G111" s="51" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -7309,7 +7306,7 @@
         <v>13791</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>45</v>
+        <v>324</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>5</v>
@@ -7347,7 +7344,7 @@
         <v>13805</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>5</v>
@@ -7366,7 +7363,7 @@
         <v>13812</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>5</v>
@@ -7404,7 +7401,7 @@
         <v>13826</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>1</v>
@@ -7423,7 +7420,7 @@
         <v>13833</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>5</v>
@@ -7440,10 +7437,10 @@
       <c r="A119" s="47"/>
       <c r="B119" s="3"/>
       <c r="C119" s="20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D119" s="21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E119" s="22">
         <f>SUM(E111:E118)</f>
@@ -7457,7 +7454,7 @@
     </row>
     <row r="120" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="28" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B120" s="9">
         <v>1938</v>
@@ -7466,13 +7463,13 @@
         <v>0</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E120" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F120" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G120" s="9" t="s">
         <v>8</v>
@@ -7480,13 +7477,13 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="45" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B121" s="2">
         <v>14148</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>5</v>
@@ -7498,7 +7495,7 @@
         <v>6</v>
       </c>
       <c r="G121" s="51" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -7507,7 +7504,7 @@
         <v>14155</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>5</v>
@@ -7526,7 +7523,7 @@
         <v>14162</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>45</v>
+        <v>324</v>
       </c>
       <c r="D123" s="3" t="s">
         <v>5</v>
@@ -7564,7 +7561,7 @@
         <v>14176</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>5</v>
@@ -7583,7 +7580,7 @@
         <v>14183</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D126" s="3" t="s">
         <v>5</v>
@@ -7621,7 +7618,7 @@
         <v>14197</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>5</v>
@@ -7638,10 +7635,10 @@
       <c r="A129" s="46"/>
       <c r="B129" s="3"/>
       <c r="C129" s="20" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D129" s="21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E129" s="22">
         <f>SUM(E121:E128)</f>
@@ -7655,7 +7652,7 @@
     </row>
     <row r="130" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="28" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B130" s="9">
         <v>1939</v>
@@ -7664,21 +7661,21 @@
         <v>0</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E130" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F130" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G130" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="45" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B131" s="2">
         <v>14512</v>
@@ -7696,7 +7693,7 @@
         <v>7</v>
       </c>
       <c r="G131" s="51" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -7724,7 +7721,7 @@
         <v>14526</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>5</v>
@@ -7743,7 +7740,7 @@
         <v>14533</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>5</v>
@@ -7781,7 +7778,7 @@
         <v>14547</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D136" s="3" t="s">
         <v>5</v>
@@ -7800,7 +7797,7 @@
         <v>14554</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>5</v>
@@ -7819,7 +7816,7 @@
         <v>14561</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D138" s="3"/>
       <c r="E138" s="8"/>
@@ -7830,10 +7827,10 @@
       <c r="A139" s="46"/>
       <c r="B139" s="3"/>
       <c r="C139" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D139" s="20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E139" s="33">
         <f>SUM(E131:E137)</f>
@@ -7847,7 +7844,7 @@
     </row>
     <row r="140" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="28" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B140" s="9">
         <v>1940</v>
@@ -7856,13 +7853,13 @@
         <v>0</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E140" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F140" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G140" s="9" t="s">
         <v>8</v>
@@ -7870,13 +7867,13 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="45" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B141" s="2">
         <v>14883</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D141" s="3" t="s">
         <v>5</v>
@@ -7888,7 +7885,7 @@
         <v>37</v>
       </c>
       <c r="G141" s="51" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -7954,7 +7951,7 @@
         <v>14911</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D145" s="3" t="s">
         <v>5</v>
@@ -7973,7 +7970,7 @@
         <v>14918</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D146" s="3" t="s">
         <v>5</v>
@@ -7992,7 +7989,7 @@
         <v>14925</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D147" s="3" t="s">
         <v>5</v>
@@ -8009,10 +8006,10 @@
       <c r="A148" s="46"/>
       <c r="B148" s="3"/>
       <c r="C148" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D148" s="20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E148" s="33">
         <f>SUM(E141:E147)</f>
@@ -8026,7 +8023,7 @@
     </row>
     <row r="149" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="28" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B149" s="9">
         <v>1941</v>
@@ -8035,13 +8032,13 @@
         <v>0</v>
       </c>
       <c r="D149" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E149" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F149" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G149" s="9" t="s">
         <v>8</v>
@@ -8049,7 +8046,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="45" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B150" s="2">
         <v>15240</v>
@@ -8066,8 +8063,8 @@
       <c r="F150" s="7">
         <v>12</v>
       </c>
-      <c r="G150" s="62" t="s">
-        <v>260</v>
+      <c r="G150" s="53" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -8076,7 +8073,7 @@
         <v>15247</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D151" s="3" t="s">
         <v>1</v>
@@ -8087,7 +8084,7 @@
       <c r="F151" s="7">
         <v>0</v>
       </c>
-      <c r="G151" s="53"/>
+      <c r="G151" s="54"/>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="46"/>
@@ -8106,7 +8103,7 @@
       <c r="F152" s="7">
         <v>13</v>
       </c>
-      <c r="G152" s="53"/>
+      <c r="G152" s="54"/>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="46"/>
@@ -8125,7 +8122,7 @@
       <c r="F153" s="7">
         <v>0</v>
       </c>
-      <c r="G153" s="53"/>
+      <c r="G153" s="54"/>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="46"/>
@@ -8144,7 +8141,7 @@
       <c r="F154" s="7">
         <v>31</v>
       </c>
-      <c r="G154" s="53"/>
+      <c r="G154" s="54"/>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="46"/>
@@ -8163,7 +8160,7 @@
       <c r="F155" s="7">
         <v>13</v>
       </c>
-      <c r="G155" s="53"/>
+      <c r="G155" s="54"/>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="46"/>
@@ -8171,7 +8168,7 @@
         <v>15282</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D156" s="3" t="s">
         <v>5</v>
@@ -8182,7 +8179,7 @@
       <c r="F156" s="7">
         <v>21</v>
       </c>
-      <c r="G156" s="53"/>
+      <c r="G156" s="54"/>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="46"/>
@@ -8190,7 +8187,7 @@
         <v>15289</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>5</v>
@@ -8201,16 +8198,16 @@
       <c r="F157" s="7">
         <v>38</v>
       </c>
-      <c r="G157" s="53"/>
+      <c r="G157" s="54"/>
     </row>
     <row r="158" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="47"/>
       <c r="B158" s="3"/>
       <c r="C158" s="20" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D158" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E158" s="22">
         <f>SUM(E150:E157)</f>
@@ -8220,11 +8217,11 @@
         <f>SUM(F150:F157)</f>
         <v>128</v>
       </c>
-      <c r="G158" s="54"/>
+      <c r="G158" s="55"/>
     </row>
     <row r="159" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="28" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B159" s="9">
         <v>1942</v>
@@ -8233,13 +8230,13 @@
         <v>0</v>
       </c>
       <c r="D159" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E159" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F159" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G159" s="9" t="s">
         <v>8</v>
@@ -8247,13 +8244,13 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="45" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B160" s="2">
         <v>15618</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>5</v>
@@ -8264,8 +8261,8 @@
       <c r="F160" s="5">
         <v>7</v>
       </c>
-      <c r="G160" s="61" t="s">
-        <v>300</v>
+      <c r="G160" s="52" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -8274,7 +8271,7 @@
         <v>15625</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D161" s="3" t="s">
         <v>5</v>
@@ -8293,7 +8290,7 @@
         <v>15632</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D162" s="3" t="s">
         <v>1</v>
@@ -8369,7 +8366,7 @@
         <v>15660</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D166" s="3" t="s">
         <v>5</v>
@@ -8388,7 +8385,7 @@
         <v>15667</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D167" s="3"/>
       <c r="E167" s="8"/>
@@ -8399,10 +8396,10 @@
       <c r="A168" s="47"/>
       <c r="B168" s="3"/>
       <c r="C168" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D168" s="21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E168" s="33">
         <f>SUM(E160:E167)</f>
@@ -8416,7 +8413,7 @@
     </row>
     <row r="169" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="28" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B169" s="9">
         <v>1943</v>
@@ -8425,13 +8422,13 @@
         <v>0</v>
       </c>
       <c r="D169" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E169" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F169" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G169" s="9" t="s">
         <v>8</v>
@@ -8439,13 +8436,13 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="45" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B170" s="2">
         <v>15975</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>1</v>
@@ -8456,8 +8453,8 @@
       <c r="F170" s="5">
         <v>12</v>
       </c>
-      <c r="G170" s="61" t="s">
-        <v>301</v>
+      <c r="G170" s="52" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -8466,7 +8463,7 @@
         <v>15982</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D171" s="3" t="s">
         <v>1</v>
@@ -8485,7 +8482,7 @@
         <v>15989</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D172" s="3" t="s">
         <v>5</v>
@@ -8523,7 +8520,7 @@
         <v>16003</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D174" s="3" t="s">
         <v>5</v>
@@ -8597,10 +8594,10 @@
       <c r="A178" s="47"/>
       <c r="B178" s="3"/>
       <c r="C178" s="20" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D178" s="21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E178" s="33">
         <f>SUM(E170:E177)</f>
@@ -8614,7 +8611,7 @@
     </row>
     <row r="179" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="28" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B179" s="9">
         <v>1944</v>
@@ -8623,13 +8620,13 @@
         <v>0</v>
       </c>
       <c r="D179" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E179" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F179" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G179" s="9" t="s">
         <v>8</v>
@@ -8637,7 +8634,7 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="45" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B180" s="2">
         <v>16346</v>
@@ -8655,7 +8652,7 @@
         <v>19</v>
       </c>
       <c r="G180" s="51" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -8664,7 +8661,7 @@
         <v>16353</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D181" s="3" t="s">
         <v>5</v>
@@ -8683,7 +8680,7 @@
         <v>16360</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D182" s="3" t="s">
         <v>5</v>
@@ -8702,7 +8699,7 @@
         <v>16367</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D183" s="3" t="s">
         <v>5</v>
@@ -8721,7 +8718,7 @@
         <v>16374</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D184" s="3" t="s">
         <v>5</v>
@@ -8759,7 +8756,7 @@
         <v>16388</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D186" s="3" t="s">
         <v>5</v>
@@ -8795,7 +8792,7 @@
       <c r="A188" s="47"/>
       <c r="B188" s="3"/>
       <c r="C188" s="20" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D188" s="21" t="s">
         <v>20</v>
@@ -8812,7 +8809,7 @@
     </row>
     <row r="189" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="28" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B189" s="9">
         <v>1945</v>
@@ -8821,13 +8818,13 @@
         <v>0</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E189" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F189" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G189" s="9" t="s">
         <v>8</v>
@@ -8835,7 +8832,7 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="45" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B190" s="2">
         <v>16710</v>
@@ -8852,8 +8849,8 @@
       <c r="F190" s="5">
         <v>26</v>
       </c>
-      <c r="G190" s="61" t="s">
-        <v>302</v>
+      <c r="G190" s="52" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -8881,7 +8878,7 @@
         <v>16724</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>1</v>
@@ -8900,7 +8897,7 @@
         <v>16731</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D193" s="3" t="s">
         <v>1</v>
@@ -8919,7 +8916,7 @@
         <v>16738</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D194" s="3" t="s">
         <v>5</v>
@@ -8938,7 +8935,7 @@
         <v>16745</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D195" s="3" t="s">
         <v>1</v>
@@ -8993,10 +8990,10 @@
       <c r="A198" s="47"/>
       <c r="B198" s="3"/>
       <c r="C198" s="20" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D198" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E198" s="33">
         <f>SUM(E190:E197)</f>
@@ -9010,7 +9007,7 @@
     </row>
     <row r="199" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="28" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B199" s="9">
         <v>1946</v>
@@ -9019,21 +9016,21 @@
         <v>0</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E199" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F199" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G199" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A200" s="48" t="s">
-        <v>188</v>
+      <c r="A200" s="60" t="s">
+        <v>186</v>
       </c>
       <c r="B200" s="2">
         <v>17074</v>
@@ -9050,8 +9047,8 @@
       <c r="F200" s="5">
         <v>7</v>
       </c>
-      <c r="G200" s="60" t="s">
-        <v>324</v>
+      <c r="G200" s="59" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -9098,7 +9095,7 @@
         <v>17095</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D203" s="3" t="s">
         <v>1</v>
@@ -9117,7 +9114,7 @@
         <v>17102</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D204" s="3" t="s">
         <v>1</v>
@@ -9136,7 +9133,7 @@
         <v>17109</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D205" s="3" t="s">
         <v>1</v>
@@ -9155,7 +9152,7 @@
         <v>17116</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>1</v>
@@ -9204,7 +9201,7 @@
       <c r="F208" s="5">
         <v>7</v>
       </c>
-      <c r="G208" s="52"/>
+      <c r="G208" s="58"/>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="49"/>
@@ -9213,7 +9210,7 @@
       <c r="D209" s="3"/>
       <c r="E209" s="8"/>
       <c r="F209" s="5"/>
-      <c r="G209" s="52"/>
+      <c r="G209" s="58"/>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="49"/>
@@ -9222,16 +9219,16 @@
       <c r="D210" s="3"/>
       <c r="E210" s="8"/>
       <c r="F210" s="5"/>
-      <c r="G210" s="52"/>
+      <c r="G210" s="58"/>
     </row>
     <row r="211" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="50"/>
       <c r="B211" s="3"/>
       <c r="C211" s="20" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D211" s="21" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E211" s="33">
         <f>SUM(E200:E208)</f>
@@ -9241,11 +9238,11 @@
         <f>SUM(F200:F208)</f>
         <v>16</v>
       </c>
-      <c r="G211" s="52"/>
+      <c r="G211" s="58"/>
     </row>
     <row r="212" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="28" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B212" s="9">
         <v>1947</v>
@@ -9254,13 +9251,13 @@
         <v>0</v>
       </c>
       <c r="D212" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E212" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F212" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G212" s="9" t="s">
         <v>8</v>
@@ -9268,13 +9265,13 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="45" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B213" s="2">
         <v>17431</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D213" s="3" t="s">
         <v>5</v>
@@ -9285,8 +9282,8 @@
       <c r="F213" s="7">
         <v>13</v>
       </c>
-      <c r="G213" s="61" t="s">
-        <v>317</v>
+      <c r="G213" s="52" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -9314,7 +9311,7 @@
         <v>17445</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D215" s="3" t="s">
         <v>5</v>
@@ -9352,7 +9349,7 @@
         <v>17459</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D217" s="3" t="s">
         <v>1</v>
@@ -9371,7 +9368,7 @@
         <v>17466</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>5</v>
@@ -9390,7 +9387,7 @@
         <v>17473</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D219" s="3" t="s">
         <v>1</v>
@@ -9409,7 +9406,7 @@
         <v>17480</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D220" s="3" t="s">
         <v>5</v>
@@ -9445,7 +9442,7 @@
       <c r="A222" s="47"/>
       <c r="B222" s="3"/>
       <c r="C222" s="20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D222" s="21" t="s">
         <v>12</v>
@@ -9462,7 +9459,7 @@
     </row>
     <row r="223" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="28" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B223" s="9">
         <v>1948</v>
@@ -9471,21 +9468,21 @@
         <v>0</v>
       </c>
       <c r="D223" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E223" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F223" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G223" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A224" s="59" t="s">
-        <v>190</v>
+      <c r="A224" s="56" t="s">
+        <v>188</v>
       </c>
       <c r="B224" s="2">
         <v>17795</v>
@@ -9503,16 +9500,16 @@
         <v>6</v>
       </c>
       <c r="G224" s="51" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A225" s="58"/>
+      <c r="A225" s="57"/>
       <c r="B225" s="2">
         <v>17802</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D225" s="3" t="s">
         <v>1</v>
@@ -9526,7 +9523,7 @@
       <c r="G225" s="51"/>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A226" s="58"/>
+      <c r="A226" s="57"/>
       <c r="B226" s="4">
         <v>17809</v>
       </c>
@@ -9545,12 +9542,12 @@
       <c r="G226" s="51"/>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A227" s="58"/>
+      <c r="A227" s="57"/>
       <c r="B227" s="2">
         <v>17814</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D227" s="3" t="s">
         <v>1</v>
@@ -9564,12 +9561,12 @@
       <c r="G227" s="51"/>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A228" s="58"/>
+      <c r="A228" s="57"/>
       <c r="B228" s="2">
         <v>17822</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D228" s="3" t="s">
         <v>1</v>
@@ -9583,7 +9580,7 @@
       <c r="G228" s="51"/>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A229" s="58"/>
+      <c r="A229" s="57"/>
       <c r="B229" s="2">
         <v>17830</v>
       </c>
@@ -9602,7 +9599,7 @@
       <c r="G229" s="51"/>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A230" s="58"/>
+      <c r="A230" s="57"/>
       <c r="B230" s="2">
         <v>17844</v>
       </c>
@@ -9621,12 +9618,12 @@
       <c r="G230" s="51"/>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A231" s="58"/>
+      <c r="A231" s="57"/>
       <c r="B231" s="4">
         <v>17852</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D231" s="3" t="s">
         <v>4</v>
@@ -9640,7 +9637,7 @@
       <c r="G231" s="51"/>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A232" s="58"/>
+      <c r="A232" s="57"/>
       <c r="B232" s="4"/>
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
@@ -9649,7 +9646,7 @@
       <c r="G232" s="51"/>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A233" s="58"/>
+      <c r="A233" s="57"/>
       <c r="B233" s="4"/>
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
@@ -9658,10 +9655,10 @@
       <c r="G233" s="51"/>
     </row>
     <row r="234" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="58"/>
+      <c r="A234" s="57"/>
       <c r="B234" s="3"/>
       <c r="C234" s="20" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D234" s="20" t="s">
         <v>11</v>
@@ -9678,7 +9675,7 @@
     </row>
     <row r="235" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="28" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B235" s="9">
         <v>1949</v>
@@ -9687,13 +9684,13 @@
         <v>0</v>
       </c>
       <c r="D235" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E235" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F235" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G235" s="9" t="s">
         <v>8</v>
@@ -9701,7 +9698,7 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="45" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B236" s="2">
         <v>18159</v>
@@ -9719,7 +9716,7 @@
         <v>6</v>
       </c>
       <c r="G236" s="51" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
@@ -9747,7 +9744,7 @@
         <v>18173</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D238" s="3" t="s">
         <v>1</v>
@@ -9785,7 +9782,7 @@
         <v>18187</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D240" s="3" t="s">
         <v>1</v>
@@ -9804,7 +9801,7 @@
         <v>18194</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D241" s="3" t="s">
         <v>1</v>
@@ -9842,7 +9839,7 @@
         <v>18208</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D243" s="3" t="s">
         <v>1</v>
@@ -9859,7 +9856,7 @@
       <c r="A244" s="46"/>
       <c r="B244" s="3"/>
       <c r="C244" s="20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D244" s="20" t="s">
         <v>7</v>
@@ -9872,11 +9869,11 @@
         <f>SUM(F236:F243)</f>
         <v>82</v>
       </c>
-      <c r="G244" s="52"/>
+      <c r="G244" s="58"/>
     </row>
     <row r="245" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="28" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B245" s="9">
         <v>1950</v>
@@ -9885,13 +9882,13 @@
         <v>0</v>
       </c>
       <c r="D245" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E245" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F245" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G245" s="9" t="s">
         <v>8</v>
@@ -9899,7 +9896,7 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" s="45" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B246" s="2">
         <v>18523</v>
@@ -9916,8 +9913,8 @@
       <c r="F246" s="5">
         <v>31</v>
       </c>
-      <c r="G246" s="61" t="s">
-        <v>264</v>
+      <c r="G246" s="52" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -9926,7 +9923,7 @@
         <v>18528</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D247" s="3" t="s">
         <v>4</v>
@@ -9945,7 +9942,7 @@
         <v>18537</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D248" s="3" t="s">
         <v>5</v>
@@ -9964,7 +9961,7 @@
         <v>18544</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D249" s="3" t="s">
         <v>5</v>
@@ -10002,7 +9999,7 @@
         <v>18558</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D251" s="3" t="s">
         <v>1</v>
@@ -10021,7 +10018,7 @@
         <v>18572</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D252" s="3" t="s">
         <v>5</v>
@@ -10057,10 +10054,10 @@
       <c r="A254" s="47"/>
       <c r="B254" s="3"/>
       <c r="C254" s="20" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D254" s="21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E254" s="33">
         <f>SUM(E246:E253)</f>
@@ -10074,7 +10071,7 @@
     </row>
     <row r="255" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="28" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B255" s="9">
         <v>1951</v>
@@ -10083,13 +10080,13 @@
         <v>0</v>
       </c>
       <c r="D255" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E255" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F255" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G255" s="9" t="s">
         <v>8</v>
@@ -10097,13 +10094,13 @@
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" s="45" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B256" s="2">
         <v>18894</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D256" s="3" t="s">
         <v>1</v>
@@ -10115,7 +10112,7 @@
         <v>0</v>
       </c>
       <c r="G256" s="51" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -10143,7 +10140,7 @@
         <v>18908</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D258" s="3" t="s">
         <v>5</v>
@@ -10162,7 +10159,7 @@
         <v>18916</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D259" s="3" t="s">
         <v>1</v>
@@ -10219,7 +10216,7 @@
         <v>18935</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D262" s="3" t="s">
         <v>5</v>
@@ -10238,7 +10235,7 @@
         <v>18943</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D263" s="3" t="s">
         <v>5</v>
@@ -10255,10 +10252,10 @@
       <c r="A264" s="47"/>
       <c r="B264" s="3"/>
       <c r="C264" s="20" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D264" s="21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E264" s="22">
         <f>SUM(E256:E263)</f>
@@ -10272,7 +10269,7 @@
     </row>
     <row r="265" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="28" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B265" s="9">
         <v>1952</v>
@@ -10281,13 +10278,13 @@
         <v>0</v>
       </c>
       <c r="D265" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E265" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F265" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G265" s="9" t="s">
         <v>8</v>
@@ -10295,13 +10292,13 @@
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" s="45" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B266" s="2">
         <v>19256</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D266" s="3" t="s">
         <v>5</v>
@@ -10313,7 +10310,7 @@
         <v>6</v>
       </c>
       <c r="G266" s="51" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
@@ -10322,7 +10319,7 @@
         <v>19265</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D267" s="3" t="s">
         <v>4</v>
@@ -10341,7 +10338,7 @@
         <v>19272</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D268" s="3" t="s">
         <v>1</v>
@@ -10360,7 +10357,7 @@
         <v>19279</v>
       </c>
       <c r="C269" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D269" s="3"/>
       <c r="E269" s="8"/>
@@ -10373,7 +10370,7 @@
         <v>19286</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D270" s="3" t="s">
         <v>5</v>
@@ -10392,7 +10389,7 @@
         <v>19293</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D271" s="3" t="s">
         <v>5</v>
@@ -10449,10 +10446,10 @@
         <v>19314</v>
       </c>
       <c r="C274" s="20" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D274" s="21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E274" s="33">
         <f>SUM(E266:E273)</f>
@@ -10466,7 +10463,7 @@
     </row>
     <row r="275" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="28" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B275" s="9">
         <v>1953</v>
@@ -10475,13 +10472,13 @@
         <v>0</v>
       </c>
       <c r="D275" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E275" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F275" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G275" s="9" t="s">
         <v>8</v>
@@ -10489,13 +10486,13 @@
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" s="45" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B276" s="2">
         <v>19620</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D276" s="3" t="s">
         <v>1</v>
@@ -10507,7 +10504,7 @@
         <v>0</v>
       </c>
       <c r="G276" s="51" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
@@ -10535,7 +10532,7 @@
         <v>19636</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D278" s="3" t="s">
         <v>5</v>
@@ -10554,7 +10551,7 @@
         <v>19643</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D279" s="3" t="s">
         <v>1</v>
@@ -10573,7 +10570,7 @@
         <v>19657</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D280" s="3" t="s">
         <v>5</v>
@@ -10592,7 +10589,7 @@
         <v>19664</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D281" s="3" t="s">
         <v>5</v>
@@ -10628,10 +10625,10 @@
       <c r="A283" s="47"/>
       <c r="B283" s="3"/>
       <c r="C283" s="20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D283" s="21" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E283" s="33">
         <f>SUM(E276:E282)</f>
@@ -10645,7 +10642,7 @@
     </row>
     <row r="284" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="28" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B284" s="9">
         <v>1954</v>
@@ -10654,13 +10651,13 @@
         <v>0</v>
       </c>
       <c r="D284" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E284" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F284" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G284" s="9" t="s">
         <v>8</v>
@@ -10668,13 +10665,13 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="45" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B285" s="2">
         <v>19984</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D285" s="3" t="s">
         <v>5</v>
@@ -10685,8 +10682,8 @@
       <c r="F285" s="7">
         <v>19</v>
       </c>
-      <c r="G285" s="61" t="s">
-        <v>305</v>
+      <c r="G285" s="52" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
@@ -10733,7 +10730,7 @@
         <v>20007</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D288" s="3" t="s">
         <v>5</v>
@@ -10752,7 +10749,7 @@
         <v>20014</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D289" s="3" t="s">
         <v>5</v>
@@ -10771,7 +10768,7 @@
         <v>20028</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D290" s="3" t="s">
         <v>5</v>
@@ -10790,7 +10787,7 @@
         <v>20035</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D291" s="3" t="s">
         <v>1</v>
@@ -10809,7 +10806,7 @@
         <v>20042</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D292" s="3" t="s">
         <v>5</v>
@@ -10826,10 +10823,10 @@
       <c r="A293" s="47"/>
       <c r="B293" s="3"/>
       <c r="C293" s="20" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D293" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E293" s="22">
         <f>SUM(E285:E292)</f>
@@ -10843,7 +10840,7 @@
     </row>
     <row r="294" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="28" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B294" s="9">
         <v>1955</v>
@@ -10852,13 +10849,13 @@
         <v>0</v>
       </c>
       <c r="D294" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E294" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F294" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G294" s="9" t="s">
         <v>8</v>
@@ -10866,13 +10863,13 @@
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295" s="45" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B295" s="2">
         <v>20348</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D295" s="3" t="s">
         <v>5</v>
@@ -10884,7 +10881,7 @@
         <v>12</v>
       </c>
       <c r="G295" s="51" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
@@ -10893,7 +10890,7 @@
         <v>20357</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D296" s="3" t="s">
         <v>5</v>
@@ -10950,7 +10947,7 @@
         <v>20376</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D299" s="3" t="s">
         <v>5</v>
@@ -10969,7 +10966,7 @@
         <v>20384</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D300" s="3" t="s">
         <v>5</v>
@@ -10988,7 +10985,7 @@
         <v>24410</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D301" s="3" t="s">
         <v>5</v>
@@ -11007,7 +11004,7 @@
         <v>20399</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D302" s="3" t="s">
         <v>5</v>
@@ -11024,10 +11021,10 @@
       <c r="A303" s="47"/>
       <c r="B303" s="3"/>
       <c r="C303" s="20" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D303" s="20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E303" s="33">
         <f>SUM(E295:E302)</f>
@@ -11041,7 +11038,7 @@
     </row>
     <row r="304" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="28" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B304" s="9">
         <v>1956</v>
@@ -11050,13 +11047,13 @@
         <v>0</v>
       </c>
       <c r="D304" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E304" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F304" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G304" s="9" t="s">
         <v>8</v>
@@ -11064,13 +11061,13 @@
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" s="45" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B305" s="2">
         <v>20714</v>
       </c>
       <c r="C305" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D305" s="3" t="s">
         <v>5</v>
@@ -11081,8 +11078,8 @@
       <c r="F305" s="5">
         <v>12</v>
       </c>
-      <c r="G305" s="61" t="s">
-        <v>308</v>
+      <c r="G305" s="52" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
@@ -11091,7 +11088,7 @@
         <v>20721</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D306" s="3" t="s">
         <v>5</v>
@@ -11110,7 +11107,7 @@
         <v>20728</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D307" s="3" t="s">
         <v>5</v>
@@ -11167,7 +11164,7 @@
         <v>20749</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D310" s="3" t="s">
         <v>1</v>
@@ -11186,7 +11183,7 @@
         <v>20756</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D311" s="3" t="s">
         <v>5</v>
@@ -11205,7 +11202,7 @@
         <v>20770</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D312" s="3" t="s">
         <v>5</v>
@@ -11222,10 +11219,10 @@
       <c r="A313" s="47"/>
       <c r="B313" s="3"/>
       <c r="C313" s="20" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D313" s="21" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E313" s="33">
         <f>SUM(E305:E312)</f>
@@ -11239,7 +11236,7 @@
     </row>
     <row r="314" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="28" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B314" s="9">
         <v>1957</v>
@@ -11248,13 +11245,13 @@
         <v>0</v>
       </c>
       <c r="D314" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E314" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F314" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G314" s="9" t="s">
         <v>8</v>
@@ -11262,13 +11259,13 @@
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315" s="45" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B315" s="2">
         <v>21083</v>
       </c>
       <c r="C315" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D315" s="3" t="s">
         <v>5</v>
@@ -11280,7 +11277,7 @@
         <v>7</v>
       </c>
       <c r="G315" s="51" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
@@ -11289,7 +11286,7 @@
         <v>21092</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D316" s="3" t="s">
         <v>5</v>
@@ -11308,7 +11305,7 @@
         <v>21099</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D317" s="3" t="s">
         <v>5</v>
@@ -11327,7 +11324,7 @@
         <v>21106</v>
       </c>
       <c r="C318" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D318" s="3" t="s">
         <v>5</v>
@@ -11384,7 +11381,7 @@
         <v>21127</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D321" s="3" t="s">
         <v>5</v>
@@ -11403,7 +11400,7 @@
         <v>21134</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D322" s="3" t="s">
         <v>5</v>
@@ -11420,7 +11417,7 @@
       <c r="A323" s="46"/>
       <c r="B323" s="2"/>
       <c r="C323" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D323" s="3"/>
       <c r="E323" s="6"/>
@@ -11431,10 +11428,10 @@
       <c r="A324" s="47"/>
       <c r="B324" s="3"/>
       <c r="C324" s="20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D324" s="21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E324" s="22">
         <f>SUM(E315:E322)</f>
@@ -11448,7 +11445,7 @@
     </row>
     <row r="325" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="28" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B325" s="9">
         <v>1958</v>
@@ -11457,13 +11454,13 @@
         <v>0</v>
       </c>
       <c r="D325" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E325" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F325" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G325" s="9" t="s">
         <v>8</v>
@@ -11471,13 +11468,13 @@
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A326" s="45" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B326" s="2">
         <v>21447</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D326" s="3" t="s">
         <v>5</v>
@@ -11489,7 +11486,7 @@
         <v>18</v>
       </c>
       <c r="G326" s="51" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">
@@ -11498,7 +11495,7 @@
         <v>21456</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D327" s="3" t="s">
         <v>5</v>
@@ -11517,7 +11514,7 @@
         <v>21463</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D328" s="3" t="s">
         <v>5</v>
@@ -11536,7 +11533,7 @@
         <v>21470</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D329" s="3" t="s">
         <v>5</v>
@@ -11555,7 +11552,7 @@
         <v>21477</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D330" s="3" t="s">
         <v>5</v>
@@ -11612,7 +11609,7 @@
         <v>21498</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D333" s="3" t="s">
         <v>5</v>
@@ -11629,10 +11626,10 @@
       <c r="A334" s="47"/>
       <c r="B334" s="3"/>
       <c r="C334" s="20" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D334" s="21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E334" s="33">
         <f>SUM(E326:E333)</f>
@@ -11646,7 +11643,7 @@
     </row>
     <row r="335" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="28" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B335" s="9">
         <v>1959</v>
@@ -11655,13 +11652,13 @@
         <v>0</v>
       </c>
       <c r="D335" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E335" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F335" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G335" s="9" t="s">
         <v>8</v>
@@ -11669,13 +11666,13 @@
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A336" s="45" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B336" s="2">
         <v>21811</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D336" s="3" t="s">
         <v>5</v>
@@ -11687,7 +11684,7 @@
         <v>20</v>
       </c>
       <c r="G336" s="51" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.25">
@@ -11696,7 +11693,7 @@
         <v>21820</v>
       </c>
       <c r="C337" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D337" s="3" t="s">
         <v>5</v>
@@ -11715,7 +11712,7 @@
         <v>21827</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D338" s="3" t="s">
         <v>5</v>
@@ -11734,7 +11731,7 @@
         <v>21834</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D339" s="3" t="s">
         <v>5</v>
@@ -11753,7 +11750,7 @@
         <v>21841</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D340" s="3" t="s">
         <v>5</v>
@@ -11772,7 +11769,7 @@
         <v>21848</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D341" s="3" t="s">
         <v>5</v>
@@ -11827,10 +11824,10 @@
       <c r="A344" s="47"/>
       <c r="B344" s="3"/>
       <c r="C344" s="20" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D344" s="21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E344" s="33">
         <f>SUM(E336:E343)</f>
@@ -11844,7 +11841,7 @@
     </row>
     <row r="345" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="28" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B345" s="9">
         <v>1960</v>
@@ -11853,13 +11850,13 @@
         <v>0</v>
       </c>
       <c r="D345" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E345" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F345" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G345" s="9" t="s">
         <v>8</v>
@@ -11867,13 +11864,13 @@
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A346" s="45" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B346" s="2">
         <v>22175</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D346" s="3" t="s">
         <v>5</v>
@@ -11885,7 +11882,7 @@
         <v>19</v>
       </c>
       <c r="G346" s="51" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.25">
@@ -11913,7 +11910,7 @@
         <v>22191</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D348" s="3" t="s">
         <v>1</v>
@@ -11932,7 +11929,7 @@
         <v>22198</v>
       </c>
       <c r="C349" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D349" s="3" t="s">
         <v>1</v>
@@ -11951,7 +11948,7 @@
         <v>22205</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D350" s="3" t="s">
         <v>5</v>
@@ -11970,7 +11967,7 @@
         <v>22212</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D351" s="3" t="s">
         <v>5</v>
@@ -11989,7 +11986,7 @@
         <v>22219</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D352" s="3" t="s">
         <v>1</v>
@@ -12025,10 +12022,10 @@
       <c r="A354" s="47"/>
       <c r="B354" s="3"/>
       <c r="C354" s="20" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D354" s="21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E354" s="22">
         <f>SUM(E346:E353)</f>
@@ -12042,7 +12039,7 @@
     </row>
     <row r="355" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B355" s="9">
         <v>1961</v>
@@ -12051,13 +12048,13 @@
         <v>0</v>
       </c>
       <c r="D355" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E355" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F355" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G355" s="9" t="s">
         <v>8</v>
@@ -12065,7 +12062,7 @@
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A356" s="45" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B356" s="2">
         <v>22541</v>
@@ -12083,7 +12080,7 @@
         <v>6</v>
       </c>
       <c r="G356" s="51" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.25">
@@ -12092,7 +12089,7 @@
         <v>22548</v>
       </c>
       <c r="C357" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D357" s="3" t="s">
         <v>1</v>
@@ -12111,7 +12108,7 @@
         <v>22555</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D358" s="3" t="s">
         <v>5</v>
@@ -12130,7 +12127,7 @@
         <v>22562</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D359" s="3" t="s">
         <v>5</v>
@@ -12168,7 +12165,7 @@
         <v>22583</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D361" s="3" t="s">
         <v>5</v>
@@ -12187,7 +12184,7 @@
         <v>22590</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D362" s="3" t="s">
         <v>1</v>
@@ -12206,7 +12203,7 @@
         <v>22597</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D363" s="3" t="s">
         <v>5</v>
@@ -12223,10 +12220,10 @@
       <c r="A364" s="47"/>
       <c r="B364" s="3"/>
       <c r="C364" s="20" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D364" s="21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E364" s="33">
         <f>SUM(E356:E363)</f>
@@ -12240,7 +12237,7 @@
     </row>
     <row r="365" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B365" s="9">
         <v>1962</v>
@@ -12249,13 +12246,13 @@
         <v>0</v>
       </c>
       <c r="D365" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E365" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F365" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G365" s="9" t="s">
         <v>8</v>
@@ -12263,13 +12260,13 @@
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A366" s="45" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B366" s="2">
         <v>22905</v>
       </c>
       <c r="C366" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D366" s="3" t="s">
         <v>4</v>
@@ -12281,7 +12278,7 @@
         <v>7</v>
       </c>
       <c r="G366" s="51" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.25">
@@ -12290,7 +12287,7 @@
         <v>22919</v>
       </c>
       <c r="C367" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D367" s="3" t="s">
         <v>5</v>
@@ -12309,7 +12306,7 @@
         <v>22926</v>
       </c>
       <c r="C368" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D368" s="3" t="s">
         <v>1</v>
@@ -12347,7 +12344,7 @@
         <v>22940</v>
       </c>
       <c r="C370" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D370" s="3" t="s">
         <v>1</v>
@@ -12366,7 +12363,7 @@
         <v>22947</v>
       </c>
       <c r="C371" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D371" s="3" t="s">
         <v>1</v>
@@ -12385,7 +12382,7 @@
         <v>22954</v>
       </c>
       <c r="C372" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D372" s="3" t="s">
         <v>5</v>
@@ -12402,10 +12399,10 @@
       <c r="A373" s="47"/>
       <c r="B373" s="3"/>
       <c r="C373" s="20" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D373" s="21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E373" s="33">
         <f>SUM(E366:E372)</f>
@@ -12419,7 +12416,7 @@
     </row>
     <row r="374" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B374" s="9">
         <v>1963</v>
@@ -12428,13 +12425,13 @@
         <v>0</v>
       </c>
       <c r="D374" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E374" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F374" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G374" s="9" t="s">
         <v>8</v>
@@ -12442,13 +12439,13 @@
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A375" s="45" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B375" s="2">
         <v>23269</v>
       </c>
       <c r="C375" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D375" s="3" t="s">
         <v>5</v>
@@ -12460,7 +12457,7 @@
         <v>20</v>
       </c>
       <c r="G375" s="51" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.25">
@@ -12469,7 +12466,7 @@
         <v>23276</v>
       </c>
       <c r="C376" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D376" s="3" t="s">
         <v>1</v>
@@ -12488,7 +12485,7 @@
         <v>23283</v>
       </c>
       <c r="C377" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D377" s="3" t="s">
         <v>1</v>
@@ -12507,7 +12504,7 @@
         <v>23290</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D378" s="3" t="s">
         <v>1</v>
@@ -12545,7 +12542,7 @@
         <v>23304</v>
       </c>
       <c r="C380" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D380" s="3" t="s">
         <v>5</v>
@@ -12564,7 +12561,7 @@
         <v>23311</v>
       </c>
       <c r="C381" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D381" s="3" t="s">
         <v>1</v>
@@ -12581,10 +12578,10 @@
       <c r="A382" s="47"/>
       <c r="B382" s="3"/>
       <c r="C382" s="20" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D382" s="21" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E382" s="22">
         <f>SUM(E375:E381)</f>
@@ -12598,7 +12595,7 @@
     </row>
     <row r="383" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="28" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B383" s="9">
         <v>1964</v>
@@ -12607,13 +12604,13 @@
         <v>0</v>
       </c>
       <c r="D383" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E383" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F383" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G383" s="9" t="s">
         <v>8</v>
@@ -12621,13 +12618,13 @@
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A384" s="45" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B384" s="2">
         <v>23640</v>
       </c>
       <c r="C384" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D384" s="3" t="s">
         <v>4</v>
@@ -12639,7 +12636,7 @@
         <v>0</v>
       </c>
       <c r="G384" s="51" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.25">
@@ -12648,7 +12645,7 @@
         <v>23647</v>
       </c>
       <c r="C385" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D385" s="3" t="s">
         <v>5</v>
@@ -12667,7 +12664,7 @@
         <v>23654</v>
       </c>
       <c r="C386" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D386" s="3" t="s">
         <v>1</v>
@@ -12686,7 +12683,7 @@
         <v>23661</v>
       </c>
       <c r="C387" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D387" s="3" t="s">
         <v>5</v>
@@ -12705,7 +12702,7 @@
         <v>23668</v>
       </c>
       <c r="C388" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D388" s="3" t="s">
         <v>1</v>
@@ -12743,7 +12740,7 @@
         <v>23682</v>
       </c>
       <c r="C390" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D390" s="3" t="s">
         <v>1</v>
@@ -12760,10 +12757,10 @@
       <c r="A391" s="47"/>
       <c r="B391" s="3"/>
       <c r="C391" s="20" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D391" s="21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E391" s="33">
         <f>SUM(E384:E390)</f>
@@ -12777,7 +12774,7 @@
     </row>
     <row r="392" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="28" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B392" s="9">
         <v>1965</v>
@@ -12786,13 +12783,13 @@
         <v>0</v>
       </c>
       <c r="D392" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E392" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F392" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G392" s="9" t="s">
         <v>8</v>
@@ -12800,13 +12797,13 @@
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A393" s="45" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B393" s="2">
         <v>24004</v>
       </c>
       <c r="C393" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D393" s="3" t="s">
         <v>1</v>
@@ -12818,7 +12815,7 @@
         <v>6</v>
       </c>
       <c r="G393" s="51" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H393" s="44"/>
     </row>
@@ -12828,7 +12825,7 @@
         <v>24011</v>
       </c>
       <c r="C394" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D394" s="3" t="s">
         <v>1</v>
@@ -12847,7 +12844,7 @@
         <v>24018</v>
       </c>
       <c r="C395" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D395" s="3" t="s">
         <v>1</v>
@@ -12866,7 +12863,7 @@
         <v>24025</v>
       </c>
       <c r="C396" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D396" s="3" t="s">
         <v>5</v>
@@ -12885,7 +12882,7 @@
         <v>24032</v>
       </c>
       <c r="C397" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D397" s="3" t="s">
         <v>1</v>
@@ -12923,7 +12920,7 @@
         <v>24046</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D399" s="3" t="s">
         <v>5</v>
@@ -12940,10 +12937,10 @@
       <c r="A400" s="47"/>
       <c r="B400" s="3"/>
       <c r="C400" s="20" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D400" s="21" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E400" s="33">
         <f>SUM(E393:E399)</f>
@@ -12957,7 +12954,7 @@
     </row>
     <row r="401" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="28" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B401" s="9">
         <v>1966</v>
@@ -12966,13 +12963,13 @@
         <v>0</v>
       </c>
       <c r="D401" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E401" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F401" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G401" s="9" t="s">
         <v>8</v>
@@ -12980,13 +12977,13 @@
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A402" s="45" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B402" s="2">
         <v>24368</v>
       </c>
       <c r="C402" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D402" s="3" t="s">
         <v>5</v>
@@ -12998,7 +12995,7 @@
         <v>19</v>
       </c>
       <c r="G402" s="51" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.25">
@@ -13007,7 +13004,7 @@
         <v>24374</v>
       </c>
       <c r="C403" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D403" s="3" t="s">
         <v>1</v>
@@ -13026,7 +13023,7 @@
         <v>24382</v>
       </c>
       <c r="C404" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D404" s="3" t="s">
         <v>1</v>
@@ -13045,7 +13042,7 @@
         <v>24389</v>
       </c>
       <c r="C405" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D405" s="3" t="s">
         <v>1</v>
@@ -13064,7 +13061,7 @@
         <v>24396</v>
       </c>
       <c r="C406" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D406" s="3" t="s">
         <v>1</v>
@@ -13083,7 +13080,7 @@
         <v>24403</v>
       </c>
       <c r="C407" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D407" s="3" t="s">
         <v>1</v>
@@ -13119,10 +13116,10 @@
       <c r="A409" s="47"/>
       <c r="B409" s="3"/>
       <c r="C409" s="20" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D409" s="21" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E409" s="22">
         <f>SUM(E402:E408)</f>
@@ -13136,7 +13133,7 @@
     </row>
     <row r="410" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="28" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B410" s="9">
         <v>1967</v>
@@ -13145,13 +13142,13 @@
         <v>0</v>
       </c>
       <c r="D410" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E410" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F410" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G410" s="9" t="s">
         <v>8</v>
@@ -13159,13 +13156,13 @@
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A411" s="45" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B411" s="2">
         <v>24732</v>
       </c>
       <c r="C411" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D411" s="3" t="s">
         <v>1</v>
@@ -13177,7 +13174,7 @@
         <v>6</v>
       </c>
       <c r="G411" s="51" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.25">
@@ -13205,7 +13202,7 @@
         <v>24746</v>
       </c>
       <c r="C413" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D413" s="3" t="s">
         <v>1</v>
@@ -13224,7 +13221,7 @@
         <v>24753</v>
       </c>
       <c r="C414" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D414" s="3" t="s">
         <v>5</v>
@@ -13243,7 +13240,7 @@
         <v>24760</v>
       </c>
       <c r="C415" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D415" s="3" t="s">
         <v>5</v>
@@ -13262,7 +13259,7 @@
         <v>24767</v>
       </c>
       <c r="C416" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D416" s="3" t="s">
         <v>1</v>
@@ -13281,7 +13278,7 @@
         <v>24774</v>
       </c>
       <c r="C417" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D417" s="3" t="s">
         <v>5</v>
@@ -13300,7 +13297,7 @@
         <v>24781</v>
       </c>
       <c r="C418" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D418" s="3" t="s">
         <v>5</v>
@@ -13317,10 +13314,10 @@
       <c r="A419" s="47"/>
       <c r="B419" s="3"/>
       <c r="C419" s="20" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D419" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E419" s="33">
         <f>SUM(E411:E418)</f>
@@ -13334,7 +13331,7 @@
     </row>
     <row r="420" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="28" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B420" s="9">
         <v>1968</v>
@@ -13343,13 +13340,13 @@
         <v>0</v>
       </c>
       <c r="D420" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E420" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F420" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G420" s="9" t="s">
         <v>8</v>
@@ -13357,13 +13354,13 @@
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A421" s="45" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B421" s="2">
         <v>25096</v>
       </c>
       <c r="C421" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D421" s="3" t="s">
         <v>5</v>
@@ -13375,7 +13372,7 @@
         <v>14</v>
       </c>
       <c r="G421" s="51" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.25">
@@ -13384,7 +13381,7 @@
         <v>25103</v>
       </c>
       <c r="C422" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D422" s="3" t="s">
         <v>5</v>
@@ -13422,7 +13419,7 @@
         <v>25117</v>
       </c>
       <c r="C424" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D424" s="3" t="s">
         <v>5</v>
@@ -13441,7 +13438,7 @@
         <v>25124</v>
       </c>
       <c r="C425" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D425" s="3" t="s">
         <v>1</v>
@@ -13460,7 +13457,7 @@
         <v>25131</v>
       </c>
       <c r="C426" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D426" s="3" t="s">
         <v>5</v>
@@ -13479,7 +13476,7 @@
         <v>25138</v>
       </c>
       <c r="C427" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D427" s="3" t="s">
         <v>5</v>
@@ -13498,7 +13495,7 @@
         <v>25145</v>
       </c>
       <c r="C428" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D428" s="3" t="s">
         <v>5</v>
@@ -13515,10 +13512,10 @@
       <c r="A429" s="47"/>
       <c r="B429" s="2"/>
       <c r="C429" s="20" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D429" s="21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E429" s="33">
         <f>SUM(E421:E428)</f>
@@ -13532,7 +13529,7 @@
     </row>
     <row r="430" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="28" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B430" s="9">
         <v>1969</v>
@@ -13541,13 +13538,13 @@
         <v>0</v>
       </c>
       <c r="D430" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E430" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F430" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G430" s="9" t="s">
         <v>8</v>
@@ -13555,13 +13552,13 @@
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A431" s="45" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B431" s="4">
         <v>25460</v>
       </c>
       <c r="C431" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D431" s="3" t="s">
         <v>5</v>
@@ -13573,7 +13570,7 @@
         <v>38</v>
       </c>
       <c r="G431" s="51" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.25">
@@ -13601,7 +13598,7 @@
         <v>25474</v>
       </c>
       <c r="C433" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D433" s="3" t="s">
         <v>1</v>
@@ -13620,7 +13617,7 @@
         <v>25479</v>
       </c>
       <c r="C434" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D434" s="3" t="s">
         <v>1</v>
@@ -13639,7 +13636,7 @@
         <v>25488</v>
       </c>
       <c r="C435" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D435" s="3" t="s">
         <v>1</v>
@@ -13658,7 +13655,7 @@
         <v>25495</v>
       </c>
       <c r="C436" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D436" s="3" t="s">
         <v>1</v>
@@ -13677,7 +13674,7 @@
         <v>25500</v>
       </c>
       <c r="C437" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D437" s="3" t="s">
         <v>4</v>
@@ -13696,7 +13693,7 @@
         <v>25509</v>
       </c>
       <c r="C438" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D438" s="3" t="s">
         <v>1</v>
@@ -13731,10 +13728,10 @@
       <c r="A441" s="47"/>
       <c r="B441" s="3"/>
       <c r="C441" s="20" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D441" s="21" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E441" s="22">
         <f>SUM(E431:E438)</f>
@@ -13748,7 +13745,7 @@
     </row>
     <row r="442" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="28" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B442" s="9">
         <v>1970</v>
@@ -13757,13 +13754,13 @@
         <v>0</v>
       </c>
       <c r="D442" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E442" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F442" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G442" s="9" t="s">
         <v>8</v>
@@ -13771,13 +13768,13 @@
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A443" s="45" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B443" s="2">
         <v>25831</v>
       </c>
       <c r="C443" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D443" s="3" t="s">
         <v>1</v>
@@ -13789,7 +13786,7 @@
         <v>6</v>
       </c>
       <c r="G443" s="51" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.25">
@@ -13798,7 +13795,7 @@
         <v>25837</v>
       </c>
       <c r="C444" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D444" s="3" t="s">
         <v>5</v>
@@ -13836,7 +13833,7 @@
         <v>25850</v>
       </c>
       <c r="C446" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D446" s="3" t="s">
         <v>1</v>
@@ -13855,7 +13852,7 @@
         <v>25858</v>
       </c>
       <c r="C447" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D447" s="3" t="s">
         <v>1</v>
@@ -13874,7 +13871,7 @@
         <v>25865</v>
       </c>
       <c r="C448" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D448" s="3" t="s">
         <v>1</v>
@@ -13893,7 +13890,7 @@
         <v>25873</v>
       </c>
       <c r="C449" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D449" s="3" t="s">
         <v>1</v>
@@ -13912,7 +13909,7 @@
         <v>25880</v>
       </c>
       <c r="C450" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D450" s="3" t="s">
         <v>1</v>
@@ -13929,10 +13926,10 @@
       <c r="A451" s="47"/>
       <c r="B451" s="3"/>
       <c r="C451" s="20" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D451" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E451" s="33">
         <f>SUM(E443:E450)</f>
@@ -13946,7 +13943,7 @@
     </row>
     <row r="452" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="28" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B452" s="9">
         <v>1971</v>
@@ -13955,27 +13952,27 @@
         <v>0</v>
       </c>
       <c r="D452" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E452" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F452" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G452" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A453" s="45" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B453" s="2">
         <v>26195</v>
       </c>
       <c r="C453" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D453" s="3" t="s">
         <v>4</v>
@@ -13987,7 +13984,7 @@
         <v>0</v>
       </c>
       <c r="G453" s="51" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.25">
@@ -13996,7 +13993,7 @@
         <v>26202</v>
       </c>
       <c r="C454" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D454" s="3" t="s">
         <v>5</v>
@@ -14015,7 +14012,7 @@
         <v>26208</v>
       </c>
       <c r="C455" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D455" s="3" t="s">
         <v>5</v>
@@ -14034,7 +14031,7 @@
         <v>26216</v>
       </c>
       <c r="C456" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D456" s="3" t="s">
         <v>1</v>
@@ -14053,7 +14050,7 @@
         <v>26221</v>
       </c>
       <c r="C457" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D457" s="3" t="s">
         <v>5</v>
@@ -14072,7 +14069,7 @@
         <v>26230</v>
       </c>
       <c r="C458" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D458" s="3" t="s">
         <v>4</v>
@@ -14091,7 +14088,7 @@
         <v>26235</v>
       </c>
       <c r="C459" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D459" s="3" t="s">
         <v>1</v>
@@ -14110,7 +14107,7 @@
         <v>26242</v>
       </c>
       <c r="C460" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D460" s="3" t="s">
         <v>5</v>
@@ -14127,10 +14124,10 @@
       <c r="A461" s="47"/>
       <c r="B461" s="3"/>
       <c r="C461" s="20" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D461" s="21" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E461" s="33">
         <f>SUM(E453:E460)</f>
@@ -14144,7 +14141,7 @@
     </row>
     <row r="462" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="28" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B462" s="9">
         <v>1972</v>
@@ -14153,13 +14150,13 @@
         <v>0</v>
       </c>
       <c r="D462" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E462" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F462" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G462" s="9" t="s">
         <v>8</v>
@@ -14167,13 +14164,13 @@
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A463" s="45" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B463" s="2">
         <v>26559</v>
       </c>
       <c r="C463" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D463" s="3" t="s">
         <v>5</v>
@@ -14185,7 +14182,7 @@
         <v>28</v>
       </c>
       <c r="G463" s="51" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.25">
@@ -14194,7 +14191,7 @@
         <v>26564</v>
       </c>
       <c r="C464" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D464" s="3" t="s">
         <v>1</v>
@@ -14213,7 +14210,7 @@
         <v>26572</v>
       </c>
       <c r="C465" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D465" s="3" t="s">
         <v>5</v>
@@ -14232,7 +14229,7 @@
         <v>26579</v>
       </c>
       <c r="C466" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D466" s="3" t="s">
         <v>5</v>
@@ -14251,7 +14248,7 @@
         <v>26586</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D467" s="3" t="s">
         <v>5</v>
@@ -14270,7 +14267,7 @@
         <v>26593</v>
       </c>
       <c r="C468" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D468" s="3" t="s">
         <v>5</v>
@@ -14289,7 +14286,7 @@
         <v>26601</v>
       </c>
       <c r="C469" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D469" s="3" t="s">
         <v>1</v>
@@ -14308,7 +14305,7 @@
         <v>26606</v>
       </c>
       <c r="C470" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D470" s="3" t="s">
         <v>5</v>
@@ -14325,7 +14322,7 @@
       <c r="A471" s="47"/>
       <c r="B471" s="3"/>
       <c r="C471" s="20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D471" s="21" t="s">
         <v>20</v>
@@ -14342,7 +14339,7 @@
     </row>
     <row r="472" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="28" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B472" s="9">
         <v>1973</v>
@@ -14351,13 +14348,13 @@
         <v>0</v>
       </c>
       <c r="D472" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E472" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F472" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G472" s="9" t="s">
         <v>8</v>
@@ -14365,13 +14362,13 @@
     </row>
     <row r="473" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A473" s="45" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B473" s="2">
         <v>26922</v>
       </c>
       <c r="C473" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D473" s="3" t="s">
         <v>5</v>
@@ -14382,8 +14379,8 @@
       <c r="F473" s="5">
         <v>19</v>
       </c>
-      <c r="G473" s="61" t="s">
-        <v>315</v>
+      <c r="G473" s="52" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="474" spans="1:7" x14ac:dyDescent="0.25">
@@ -14392,7 +14389,7 @@
         <v>26929</v>
       </c>
       <c r="C474" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D474" s="3" t="s">
         <v>5</v>
@@ -14430,7 +14427,7 @@
         <v>26943</v>
       </c>
       <c r="C476" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D476" s="3" t="s">
         <v>1</v>
@@ -14449,7 +14446,7 @@
         <v>26949</v>
       </c>
       <c r="C477" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D477" s="3" t="s">
         <v>1</v>
@@ -14468,7 +14465,7 @@
         <v>26958</v>
       </c>
       <c r="C478" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D478" s="3" t="s">
         <v>5</v>
@@ -14487,7 +14484,7 @@
         <v>26963</v>
       </c>
       <c r="C479" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D479" s="3" t="s">
         <v>1</v>
@@ -14506,7 +14503,7 @@
         <v>26971</v>
       </c>
       <c r="C480" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D480" s="3" t="s">
         <v>5</v>
@@ -14523,10 +14520,10 @@
       <c r="A481" s="47"/>
       <c r="B481" s="3"/>
       <c r="C481" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D481" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E481" s="33">
         <f>SUM(E473:E480)</f>
@@ -14540,7 +14537,7 @@
     </row>
     <row r="482" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="28" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B482" s="9">
         <v>1974</v>
@@ -14549,13 +14546,13 @@
         <v>0</v>
       </c>
       <c r="D482" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E482" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F482" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G482" s="9" t="s">
         <v>8</v>
@@ -14563,13 +14560,13 @@
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A483" s="45" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B483" s="2">
         <v>27285</v>
       </c>
       <c r="C483" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D483" s="3" t="s">
         <v>4</v>
@@ -14581,7 +14578,7 @@
         <v>6</v>
       </c>
       <c r="G483" s="51" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.25">
@@ -14609,7 +14606,7 @@
         <v>27300</v>
       </c>
       <c r="C485" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D485" s="3" t="s">
         <v>1</v>
@@ -14628,7 +14625,7 @@
         <v>27306</v>
       </c>
       <c r="C486" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D486" s="3" t="s">
         <v>1</v>
@@ -14647,7 +14644,7 @@
         <v>27313</v>
       </c>
       <c r="C487" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D487" s="3" t="s">
         <v>1</v>
@@ -14666,7 +14663,7 @@
         <v>27320</v>
       </c>
       <c r="C488" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D488" s="3" t="s">
         <v>1</v>
@@ -14685,7 +14682,7 @@
         <v>27327</v>
       </c>
       <c r="C489" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D489" s="3" t="s">
         <v>5</v>
@@ -14704,7 +14701,7 @@
         <v>27336</v>
       </c>
       <c r="C490" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D490" s="3" t="s">
         <v>1</v>
@@ -14721,7 +14718,7 @@
       <c r="A491" s="47"/>
       <c r="B491" s="3"/>
       <c r="C491" s="20" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D491" s="21" t="s">
         <v>7</v>
@@ -14738,7 +14735,7 @@
     </row>
     <row r="492" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="28" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B492" s="9">
         <v>1975</v>
@@ -14747,13 +14744,13 @@
         <v>0</v>
       </c>
       <c r="D492" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E492" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F492" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G492" s="9" t="s">
         <v>8</v>
@@ -14761,13 +14758,13 @@
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A493" s="45" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B493" s="2">
         <v>27650</v>
       </c>
       <c r="C493" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D493" s="3" t="s">
         <v>1</v>
@@ -14779,7 +14776,7 @@
         <v>6</v>
       </c>
       <c r="G493" s="51" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.25">
@@ -14788,7 +14785,7 @@
         <v>27656</v>
       </c>
       <c r="C494" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D494" s="3" t="s">
         <v>1</v>
@@ -14807,7 +14804,7 @@
         <v>27663</v>
       </c>
       <c r="C495" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D495" s="3" t="s">
         <v>5</v>
@@ -14826,7 +14823,7 @@
         <v>27671</v>
       </c>
       <c r="C496" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D496" s="3" t="s">
         <v>5</v>
@@ -14845,7 +14842,7 @@
         <v>27678</v>
       </c>
       <c r="C497" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D497" s="3" t="s">
         <v>1</v>
@@ -14864,7 +14861,7 @@
         <v>27685</v>
       </c>
       <c r="C498" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D498" s="3" t="s">
         <v>1</v>
@@ -14883,7 +14880,7 @@
         <v>27692</v>
       </c>
       <c r="C499" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D499" s="3" t="s">
         <v>1</v>
@@ -14902,7 +14899,7 @@
         <v>27700</v>
       </c>
       <c r="C500" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D500" s="3" t="s">
         <v>5</v>
@@ -14919,10 +14916,10 @@
       <c r="A501" s="47"/>
       <c r="B501" s="3"/>
       <c r="C501" s="20" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D501" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E501" s="33">
         <f t="shared" ref="E501:F501" si="1">SUM(E493:E500)</f>
@@ -14936,7 +14933,7 @@
     </row>
     <row r="502" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="28" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B502" s="9">
         <v>1976</v>
@@ -14945,27 +14942,27 @@
         <v>0</v>
       </c>
       <c r="D502" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E502" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F502" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G502" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A503" s="63" t="s">
-        <v>218</v>
+      <c r="A503" s="48" t="s">
+        <v>216</v>
       </c>
       <c r="B503" s="2">
         <v>28021</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D503" s="3" t="s">
         <v>1</v>
@@ -14977,7 +14974,7 @@
         <v>0</v>
       </c>
       <c r="G503" s="51" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.25">
@@ -14986,7 +14983,7 @@
         <v>28029</v>
       </c>
       <c r="C504" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D504" s="3" t="s">
         <v>5</v>
@@ -15005,7 +15002,7 @@
         <v>28035</v>
       </c>
       <c r="C505" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D505" s="3" t="s">
         <v>1</v>
@@ -15024,7 +15021,7 @@
         <v>28042</v>
       </c>
       <c r="C506" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D506" s="3" t="s">
         <v>1</v>
@@ -15043,7 +15040,7 @@
         <v>28050</v>
       </c>
       <c r="C507" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D507" s="3" t="s">
         <v>1</v>
@@ -15062,7 +15059,7 @@
         <v>28055</v>
       </c>
       <c r="C508" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D508" s="3" t="s">
         <v>1</v>
@@ -15081,7 +15078,7 @@
         <v>28063</v>
       </c>
       <c r="C509" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D509" s="3" t="s">
         <v>1</v>
@@ -15100,7 +15097,7 @@
         <v>28070</v>
       </c>
       <c r="C510" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D510" s="3" t="s">
         <v>1</v>
@@ -15119,7 +15116,7 @@
         <v>28077</v>
       </c>
       <c r="C511" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D511" s="3" t="s">
         <v>1</v>
@@ -15181,10 +15178,10 @@
       <c r="A517" s="50"/>
       <c r="B517" s="3"/>
       <c r="C517" s="20" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D517" s="21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E517" s="33">
         <f>SUM(E503:E511)</f>
@@ -15198,7 +15195,7 @@
     </row>
     <row r="518" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="28" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B518" s="9">
         <v>1977</v>
@@ -15207,13 +15204,13 @@
         <v>0</v>
       </c>
       <c r="D518" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E518" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F518" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G518" s="9" t="s">
         <v>8</v>
@@ -15221,13 +15218,13 @@
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A519" s="45" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B519" s="2">
         <v>28378</v>
       </c>
       <c r="C519" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D519" s="3" t="s">
         <v>5</v>
@@ -15239,7 +15236,7 @@
         <v>12</v>
       </c>
       <c r="G519" s="51" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.25">
@@ -15248,7 +15245,7 @@
         <v>28386</v>
       </c>
       <c r="C520" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D520" s="3" t="s">
         <v>5</v>
@@ -15267,7 +15264,7 @@
         <v>28392</v>
       </c>
       <c r="C521" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D521" s="3" t="s">
         <v>5</v>
@@ -15286,7 +15283,7 @@
         <v>28400</v>
       </c>
       <c r="C522" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D522" s="3" t="s">
         <v>5</v>
@@ -15305,7 +15302,7 @@
         <v>28407</v>
       </c>
       <c r="C523" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D523" s="3" t="s">
         <v>5</v>
@@ -15324,7 +15321,7 @@
         <v>28412</v>
       </c>
       <c r="C524" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D524" s="3" t="s">
         <v>5</v>
@@ -15343,7 +15340,7 @@
         <v>28419</v>
       </c>
       <c r="C525" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D525" s="3" t="s">
         <v>5</v>
@@ -15362,7 +15359,7 @@
         <v>28427</v>
       </c>
       <c r="C526" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D526" s="3" t="s">
         <v>1</v>
@@ -15378,10 +15375,10 @@
     <row r="527" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A527" s="46"/>
       <c r="B527" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C527" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D527" s="3" t="s">
         <v>5</v>
@@ -15398,10 +15395,10 @@
       <c r="A528" s="47"/>
       <c r="B528" s="3"/>
       <c r="C528" s="20" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D528" s="21" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E528" s="33">
         <f t="shared" ref="E528:F528" si="2">SUM(E519:E527)</f>
@@ -15415,7 +15412,7 @@
     </row>
     <row r="529" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="28" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B529" s="9">
         <v>1978</v>
@@ -15424,13 +15421,13 @@
         <v>0</v>
       </c>
       <c r="D529" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E529" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F529" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G529" s="9" t="s">
         <v>8</v>
@@ -15438,13 +15435,13 @@
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A530" s="45" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B530" s="2">
         <v>28741</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D530" s="3" t="s">
         <v>5</v>
@@ -15456,7 +15453,7 @@
         <v>40</v>
       </c>
       <c r="G530" s="51" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="531" spans="1:7" x14ac:dyDescent="0.25">
@@ -15465,7 +15462,7 @@
         <v>28749</v>
       </c>
       <c r="C531" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D531" s="3" t="s">
         <v>1</v>
@@ -15484,7 +15481,7 @@
         <v>28757</v>
       </c>
       <c r="C532" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D532" s="3" t="s">
         <v>5</v>
@@ -15503,7 +15500,7 @@
         <v>28763</v>
       </c>
       <c r="C533" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D533" s="3" t="s">
         <v>1</v>
@@ -15522,7 +15519,7 @@
         <v>28770</v>
       </c>
       <c r="C534" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D534" s="3" t="s">
         <v>5</v>
@@ -15541,7 +15538,7 @@
         <v>28776</v>
       </c>
       <c r="C535" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D535" s="3" t="s">
         <v>5</v>
@@ -15560,7 +15557,7 @@
         <v>28785</v>
       </c>
       <c r="C536" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D536" s="3" t="s">
         <v>5</v>
@@ -15579,7 +15576,7 @@
         <v>28791</v>
       </c>
       <c r="C537" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D537" s="3" t="s">
         <v>5</v>
@@ -15596,7 +15593,7 @@
       <c r="A538" s="47"/>
       <c r="B538" s="3"/>
       <c r="C538" s="20" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D538" s="21" t="s">
         <v>20</v>
@@ -15613,7 +15610,7 @@
     </row>
     <row r="539" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="28" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B539" s="9">
         <v>1979</v>
@@ -15622,13 +15619,13 @@
         <v>0</v>
       </c>
       <c r="D539" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E539" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F539" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G539" s="9" t="s">
         <v>8</v>
@@ -15636,13 +15633,13 @@
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A540" s="45" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B540" s="2">
         <v>29106</v>
       </c>
       <c r="C540" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D540" s="3" t="s">
         <v>5</v>
@@ -15654,7 +15651,7 @@
         <v>16</v>
       </c>
       <c r="G540" s="51" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.25">
@@ -15663,7 +15660,7 @@
         <v>29113</v>
       </c>
       <c r="C541" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D541" s="3" t="s">
         <v>1</v>
@@ -15682,7 +15679,7 @@
         <v>29119</v>
       </c>
       <c r="C542" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D542" s="3" t="s">
         <v>1</v>
@@ -15701,7 +15698,7 @@
         <v>29127</v>
       </c>
       <c r="C543" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D543" s="3" t="s">
         <v>1</v>
@@ -15720,7 +15717,7 @@
         <v>29134</v>
       </c>
       <c r="C544" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D544" s="3" t="s">
         <v>5</v>
@@ -15739,7 +15736,7 @@
         <v>29142</v>
       </c>
       <c r="C545" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D545" s="3" t="s">
         <v>5</v>
@@ -15758,7 +15755,7 @@
         <v>29147</v>
       </c>
       <c r="C546" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D546" s="3" t="s">
         <v>5</v>
@@ -15777,7 +15774,7 @@
         <v>29155</v>
       </c>
       <c r="C547" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D547" s="3" t="s">
         <v>5</v>
@@ -15796,7 +15793,7 @@
         <v>29161</v>
       </c>
       <c r="C548" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D548" s="3" t="s">
         <v>5</v>
@@ -15813,10 +15810,10 @@
       <c r="A549" s="47"/>
       <c r="B549" s="3"/>
       <c r="C549" s="20" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D549" s="21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E549" s="33">
         <f t="shared" ref="E549:F549" si="3">SUM(E540:E548)</f>
@@ -15830,7 +15827,7 @@
     </row>
     <row r="550" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="28" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B550" s="9">
         <v>1980</v>
@@ -15839,13 +15836,13 @@
         <v>0</v>
       </c>
       <c r="D550" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E550" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F550" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G550" s="9" t="s">
         <v>8</v>
@@ -15853,7 +15850,7 @@
     </row>
     <row r="551" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A551" s="45" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B551" s="2">
         <v>29470</v>
@@ -15871,7 +15868,7 @@
         <v>39</v>
       </c>
       <c r="G551" s="51" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.25">
@@ -15880,7 +15877,7 @@
         <v>29478</v>
       </c>
       <c r="C552" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D552" s="3" t="s">
         <v>1</v>
@@ -15899,7 +15896,7 @@
         <v>29483</v>
       </c>
       <c r="C553" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D553" s="3" t="s">
         <v>5</v>
@@ -15918,7 +15915,7 @@
         <v>29491</v>
       </c>
       <c r="C554" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D554" s="3" t="s">
         <v>5</v>
@@ -15937,7 +15934,7 @@
         <v>29498</v>
       </c>
       <c r="C555" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D555" s="3" t="s">
         <v>5</v>
@@ -15956,7 +15953,7 @@
         <v>29505</v>
       </c>
       <c r="C556" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D556" s="3" t="s">
         <v>1</v>
@@ -15975,7 +15972,7 @@
         <v>29512</v>
       </c>
       <c r="C557" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D557" s="3" t="s">
         <v>5</v>
@@ -15994,7 +15991,7 @@
         <v>29519</v>
       </c>
       <c r="C558" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D558" s="3" t="s">
         <v>5</v>
@@ -16013,7 +16010,7 @@
         <v>29525</v>
       </c>
       <c r="C559" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D559" s="3" t="s">
         <v>5</v>
@@ -16030,10 +16027,10 @@
       <c r="A560" s="47"/>
       <c r="B560" s="3"/>
       <c r="C560" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D560" s="21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E560" s="33">
         <f t="shared" ref="E560:F560" si="4">SUM(E551:E559)</f>
@@ -16047,7 +16044,7 @@
     </row>
     <row r="561" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="28" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B561" s="9">
         <v>1981</v>
@@ -16056,13 +16053,13 @@
         <v>0</v>
       </c>
       <c r="D561" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E561" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F561" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G561" s="9" t="s">
         <v>8</v>
@@ -16070,7 +16067,7 @@
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A562" s="45" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B562" s="2">
         <v>29841</v>
@@ -16088,7 +16085,7 @@
         <v>47</v>
       </c>
       <c r="G562" s="51" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.25">
@@ -16097,7 +16094,7 @@
         <v>29847</v>
       </c>
       <c r="C563" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D563" s="3" t="s">
         <v>1</v>
@@ -16116,7 +16113,7 @@
         <v>29855</v>
       </c>
       <c r="C564" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D564" s="3" t="s">
         <v>5</v>
@@ -16135,7 +16132,7 @@
         <v>29863</v>
       </c>
       <c r="C565" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D565" s="3" t="s">
         <v>5</v>
@@ -16154,7 +16151,7 @@
         <v>29869</v>
       </c>
       <c r="C566" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D566" s="3" t="s">
         <v>1</v>
@@ -16173,7 +16170,7 @@
         <v>29875</v>
       </c>
       <c r="C567" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D567" s="3" t="s">
         <v>1</v>
@@ -16192,7 +16189,7 @@
         <v>29883</v>
       </c>
       <c r="C568" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D568" s="3" t="s">
         <v>5</v>
@@ -16211,7 +16208,7 @@
         <v>29890</v>
       </c>
       <c r="C569" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D569" s="3" t="s">
         <v>5</v>
@@ -16230,7 +16227,7 @@
         <v>29897</v>
       </c>
       <c r="C570" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D570" s="3" t="s">
         <v>5</v>
@@ -16247,10 +16244,10 @@
       <c r="A571" s="47"/>
       <c r="B571" s="3"/>
       <c r="C571" s="20" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D571" s="21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E571" s="33">
         <f t="shared" ref="E571:F571" si="5">SUM(E562:E570)</f>
@@ -16264,7 +16261,7 @@
     </row>
     <row r="572" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="28" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B572" s="9">
         <v>1982</v>
@@ -16273,13 +16270,13 @@
         <v>0</v>
       </c>
       <c r="D572" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E572" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F572" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G572" s="9" t="s">
         <v>8</v>
@@ -16287,13 +16284,13 @@
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A573" s="45" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B573" s="2">
         <v>30204</v>
       </c>
       <c r="C573" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D573" s="3" t="s">
         <v>5</v>
@@ -16305,7 +16302,7 @@
         <v>36</v>
       </c>
       <c r="G573" s="51" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.25">
@@ -16314,7 +16311,7 @@
         <v>30212</v>
       </c>
       <c r="C574" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D574" s="3" t="s">
         <v>1</v>
@@ -16333,7 +16330,7 @@
         <v>30220</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D575" s="3" t="s">
         <v>5</v>
@@ -16352,7 +16349,7 @@
         <v>30233</v>
       </c>
       <c r="C576" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D576" s="3" t="s">
         <v>5</v>
@@ -16371,7 +16368,7 @@
         <v>30240</v>
       </c>
       <c r="C577" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D577" s="3" t="s">
         <v>5</v>
@@ -16390,7 +16387,7 @@
         <v>30247</v>
       </c>
       <c r="C578" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D578" s="3" t="s">
         <v>5</v>
@@ -16409,7 +16406,7 @@
         <v>30254</v>
       </c>
       <c r="C579" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D579" s="3" t="s">
         <v>5</v>
@@ -16425,10 +16422,10 @@
     <row r="580" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A580" s="46"/>
       <c r="B580" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C580" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D580" s="3" t="s">
         <v>5</v>
@@ -16445,10 +16442,10 @@
       <c r="A581" s="47"/>
       <c r="B581" s="3"/>
       <c r="C581" s="20" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D581" s="21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E581" s="33">
         <f>SUM(E573:E580)</f>
@@ -16462,7 +16459,7 @@
     </row>
     <row r="582" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="28" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B582" s="9">
         <v>1983</v>
@@ -16471,13 +16468,13 @@
         <v>0</v>
       </c>
       <c r="D582" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E582" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F582" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G582" s="9" t="s">
         <v>8</v>
@@ -16485,13 +16482,13 @@
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A583" s="45" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B583" s="2">
         <v>30570</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D583" s="3" t="s">
         <v>1</v>
@@ -16503,7 +16500,7 @@
         <v>0</v>
       </c>
       <c r="G583" s="51" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="584" spans="1:7" x14ac:dyDescent="0.25">
@@ -16512,7 +16509,7 @@
         <v>30576</v>
       </c>
       <c r="C584" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D584" s="3" t="s">
         <v>5</v>
@@ -16531,7 +16528,7 @@
         <v>30583</v>
       </c>
       <c r="C585" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D585" s="3" t="s">
         <v>5</v>
@@ -16550,7 +16547,7 @@
         <v>30589</v>
       </c>
       <c r="C586" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D586" s="3" t="s">
         <v>5</v>
@@ -16569,7 +16566,7 @@
         <v>30596</v>
       </c>
       <c r="C587" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D587" s="3" t="s">
         <v>5</v>
@@ -16588,7 +16585,7 @@
         <v>30604</v>
       </c>
       <c r="C588" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D588" s="3" t="s">
         <v>5</v>
@@ -16607,7 +16604,7 @@
         <v>30610</v>
       </c>
       <c r="C589" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D589" s="3" t="s">
         <v>5</v>
@@ -16626,7 +16623,7 @@
         <v>30617</v>
       </c>
       <c r="C590" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D590" s="3" t="s">
         <v>5</v>
@@ -16643,10 +16640,10 @@
       <c r="A591" s="47"/>
       <c r="B591" s="3"/>
       <c r="C591" s="20" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D591" s="21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E591" s="33">
         <f>SUM(E583:E590)</f>
@@ -16660,7 +16657,7 @@
     </row>
     <row r="592" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B592" s="9">
         <v>1984</v>
@@ -16669,13 +16666,13 @@
         <v>0</v>
       </c>
       <c r="D592" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E592" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F592" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G592" s="9" t="s">
         <v>8</v>
@@ -16683,13 +16680,13 @@
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A593" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B593" s="2">
         <v>30933</v>
       </c>
       <c r="C593" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D593" s="3" t="s">
         <v>5</v>
@@ -16701,7 +16698,7 @@
         <v>48</v>
       </c>
       <c r="G593" s="51" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.25">
@@ -16710,7 +16707,7 @@
         <v>30940</v>
       </c>
       <c r="C594" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D594" s="3" t="s">
         <v>5</v>
@@ -16729,7 +16726,7 @@
         <v>30946</v>
       </c>
       <c r="C595" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D595" s="3" t="s">
         <v>5</v>
@@ -16748,7 +16745,7 @@
         <v>30961</v>
       </c>
       <c r="C596" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D596" s="3" t="s">
         <v>5</v>
@@ -16767,7 +16764,7 @@
         <v>30968</v>
       </c>
       <c r="C597" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D597" s="3" t="s">
         <v>5</v>
@@ -16786,7 +16783,7 @@
         <v>30975</v>
       </c>
       <c r="C598" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D598" s="3" t="s">
         <v>5</v>
@@ -16805,7 +16802,7 @@
         <v>30982</v>
       </c>
       <c r="C599" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D599" s="3" t="s">
         <v>5</v>
@@ -16822,10 +16819,10 @@
       <c r="A600" s="47"/>
       <c r="B600" s="3"/>
       <c r="C600" s="20" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D600" s="21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E600" s="33">
         <f>SUM(E593:E599)</f>
@@ -18342,21 +18339,83 @@
     <row r="2039" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="116">
-    <mergeCell ref="A530:A538"/>
-    <mergeCell ref="A540:A549"/>
-    <mergeCell ref="A551:A560"/>
-    <mergeCell ref="A562:A571"/>
-    <mergeCell ref="A573:A581"/>
-    <mergeCell ref="A583:A591"/>
-    <mergeCell ref="A593:A600"/>
-    <mergeCell ref="A493:A501"/>
-    <mergeCell ref="A443:A451"/>
-    <mergeCell ref="A453:A461"/>
-    <mergeCell ref="A463:A471"/>
-    <mergeCell ref="A473:A481"/>
-    <mergeCell ref="A483:A491"/>
-    <mergeCell ref="A503:A517"/>
-    <mergeCell ref="A519:A528"/>
+    <mergeCell ref="A34:A43"/>
+    <mergeCell ref="A45:A54"/>
+    <mergeCell ref="A56:A64"/>
+    <mergeCell ref="G45:G54"/>
+    <mergeCell ref="G77:G89"/>
+    <mergeCell ref="G91:G99"/>
+    <mergeCell ref="G56:G64"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A11:A19"/>
+    <mergeCell ref="G2:G9"/>
+    <mergeCell ref="G34:G43"/>
+    <mergeCell ref="G11:G19"/>
+    <mergeCell ref="G21:G32"/>
+    <mergeCell ref="A21:A32"/>
+    <mergeCell ref="A66:A75"/>
+    <mergeCell ref="A91:A99"/>
+    <mergeCell ref="G66:G75"/>
+    <mergeCell ref="A101:A109"/>
+    <mergeCell ref="A77:A89"/>
+    <mergeCell ref="G224:G234"/>
+    <mergeCell ref="G236:G244"/>
+    <mergeCell ref="G200:G211"/>
+    <mergeCell ref="G213:G222"/>
+    <mergeCell ref="G180:G188"/>
+    <mergeCell ref="A180:A188"/>
+    <mergeCell ref="A111:A119"/>
+    <mergeCell ref="G101:G109"/>
+    <mergeCell ref="G121:G129"/>
+    <mergeCell ref="G141:G148"/>
+    <mergeCell ref="G131:G139"/>
+    <mergeCell ref="A236:A244"/>
+    <mergeCell ref="A170:A178"/>
+    <mergeCell ref="G160:G168"/>
+    <mergeCell ref="G190:G198"/>
+    <mergeCell ref="G170:G178"/>
+    <mergeCell ref="A190:A198"/>
+    <mergeCell ref="A200:A211"/>
+    <mergeCell ref="A213:A222"/>
+    <mergeCell ref="G305:G313"/>
+    <mergeCell ref="G266:G274"/>
+    <mergeCell ref="G276:G283"/>
+    <mergeCell ref="G285:G293"/>
+    <mergeCell ref="A266:A274"/>
+    <mergeCell ref="G111:G119"/>
+    <mergeCell ref="A150:A158"/>
+    <mergeCell ref="A141:A148"/>
+    <mergeCell ref="G150:G158"/>
+    <mergeCell ref="G246:G254"/>
+    <mergeCell ref="A246:A254"/>
+    <mergeCell ref="A276:A283"/>
+    <mergeCell ref="A131:A139"/>
+    <mergeCell ref="G256:G264"/>
+    <mergeCell ref="A256:A264"/>
+    <mergeCell ref="A121:A129"/>
+    <mergeCell ref="G295:G303"/>
+    <mergeCell ref="A295:A303"/>
+    <mergeCell ref="A285:A293"/>
+    <mergeCell ref="A224:A234"/>
+    <mergeCell ref="A160:A168"/>
+    <mergeCell ref="G346:G354"/>
+    <mergeCell ref="G356:G364"/>
+    <mergeCell ref="G315:G324"/>
+    <mergeCell ref="G326:G334"/>
+    <mergeCell ref="G336:G344"/>
+    <mergeCell ref="G573:G581"/>
+    <mergeCell ref="G583:G591"/>
+    <mergeCell ref="G593:G600"/>
+    <mergeCell ref="G551:G560"/>
+    <mergeCell ref="G562:G571"/>
+    <mergeCell ref="G384:G391"/>
+    <mergeCell ref="G519:G528"/>
+    <mergeCell ref="G530:G538"/>
+    <mergeCell ref="G540:G549"/>
+    <mergeCell ref="G493:G501"/>
+    <mergeCell ref="G503:G517"/>
+    <mergeCell ref="G411:G419"/>
+    <mergeCell ref="G421:G429"/>
     <mergeCell ref="A336:A344"/>
     <mergeCell ref="A326:A334"/>
     <mergeCell ref="A305:A313"/>
@@ -18381,83 +18440,21 @@
     <mergeCell ref="A402:A409"/>
     <mergeCell ref="A411:A419"/>
     <mergeCell ref="A421:A429"/>
-    <mergeCell ref="G346:G354"/>
-    <mergeCell ref="G356:G364"/>
-    <mergeCell ref="G315:G324"/>
-    <mergeCell ref="G326:G334"/>
-    <mergeCell ref="G336:G344"/>
-    <mergeCell ref="G573:G581"/>
-    <mergeCell ref="G583:G591"/>
-    <mergeCell ref="G593:G600"/>
-    <mergeCell ref="G551:G560"/>
-    <mergeCell ref="G562:G571"/>
-    <mergeCell ref="G384:G391"/>
-    <mergeCell ref="G519:G528"/>
-    <mergeCell ref="G530:G538"/>
-    <mergeCell ref="G540:G549"/>
-    <mergeCell ref="G493:G501"/>
-    <mergeCell ref="G503:G517"/>
-    <mergeCell ref="G411:G419"/>
-    <mergeCell ref="G421:G429"/>
-    <mergeCell ref="G305:G313"/>
-    <mergeCell ref="G266:G274"/>
-    <mergeCell ref="G276:G283"/>
-    <mergeCell ref="G285:G293"/>
-    <mergeCell ref="A266:A274"/>
-    <mergeCell ref="G111:G119"/>
-    <mergeCell ref="A150:A158"/>
-    <mergeCell ref="A141:A148"/>
-    <mergeCell ref="G150:G158"/>
-    <mergeCell ref="G246:G254"/>
-    <mergeCell ref="A246:A254"/>
-    <mergeCell ref="A276:A283"/>
-    <mergeCell ref="A131:A139"/>
-    <mergeCell ref="G256:G264"/>
-    <mergeCell ref="A256:A264"/>
-    <mergeCell ref="A121:A129"/>
-    <mergeCell ref="G295:G303"/>
-    <mergeCell ref="A295:A303"/>
-    <mergeCell ref="A285:A293"/>
-    <mergeCell ref="A224:A234"/>
-    <mergeCell ref="A160:A168"/>
-    <mergeCell ref="A101:A109"/>
-    <mergeCell ref="A77:A89"/>
-    <mergeCell ref="G224:G234"/>
-    <mergeCell ref="G236:G244"/>
-    <mergeCell ref="G200:G211"/>
-    <mergeCell ref="G213:G222"/>
-    <mergeCell ref="G180:G188"/>
-    <mergeCell ref="A180:A188"/>
-    <mergeCell ref="A111:A119"/>
-    <mergeCell ref="G101:G109"/>
-    <mergeCell ref="G121:G129"/>
-    <mergeCell ref="G141:G148"/>
-    <mergeCell ref="G131:G139"/>
-    <mergeCell ref="A236:A244"/>
-    <mergeCell ref="A170:A178"/>
-    <mergeCell ref="G160:G168"/>
-    <mergeCell ref="G190:G198"/>
-    <mergeCell ref="G170:G178"/>
-    <mergeCell ref="A190:A198"/>
-    <mergeCell ref="A200:A211"/>
-    <mergeCell ref="A213:A222"/>
-    <mergeCell ref="A34:A43"/>
-    <mergeCell ref="A45:A54"/>
-    <mergeCell ref="A56:A64"/>
-    <mergeCell ref="G45:G54"/>
-    <mergeCell ref="G77:G89"/>
-    <mergeCell ref="G91:G99"/>
-    <mergeCell ref="G56:G64"/>
-    <mergeCell ref="A2:A9"/>
-    <mergeCell ref="A11:A19"/>
-    <mergeCell ref="G2:G9"/>
-    <mergeCell ref="G34:G43"/>
-    <mergeCell ref="G11:G19"/>
-    <mergeCell ref="G21:G32"/>
-    <mergeCell ref="A21:A32"/>
-    <mergeCell ref="A66:A75"/>
-    <mergeCell ref="A91:A99"/>
-    <mergeCell ref="G66:G75"/>
+    <mergeCell ref="A530:A538"/>
+    <mergeCell ref="A540:A549"/>
+    <mergeCell ref="A551:A560"/>
+    <mergeCell ref="A562:A571"/>
+    <mergeCell ref="A573:A581"/>
+    <mergeCell ref="A583:A591"/>
+    <mergeCell ref="A593:A600"/>
+    <mergeCell ref="A493:A501"/>
+    <mergeCell ref="A443:A451"/>
+    <mergeCell ref="A453:A461"/>
+    <mergeCell ref="A463:A471"/>
+    <mergeCell ref="A473:A481"/>
+    <mergeCell ref="A483:A491"/>
+    <mergeCell ref="A503:A517"/>
+    <mergeCell ref="A519:A528"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A34:A43" r:id="rId1" display="Click here for the 1930 season football articles " xr:uid="{19CFF195-F347-4DC1-882D-E27AE52E410C}"/>
